--- a/irrdash3.xlsx
+++ b/irrdash3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.russo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A31B74C-AABC-420E-BE24-2E33F80907FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D3E71CD-6554-4BA8-AE7C-5ACE284D0AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -639,7 +639,7 @@
         <v>2026</v>
       </c>
       <c r="C4" s="5">
-        <v>3235.4861380697657</v>
+        <v>3354.9604906857189</v>
       </c>
       <c r="D4" s="5">
         <v>2346.2961342640269</v>
@@ -650,13 +650,11 @@
       <c r="F4" s="5">
         <v>6605.1316597436398</v>
       </c>
-      <c r="G4" s="5">
-        <v>1693.9837038587689</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5">
-        <v>1867.7164444544671</v>
-      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5">
+        <v>777.22850688213123</v>
+      </c>
+      <c r="I4" s="5"/>
       <c r="J4" s="5">
         <v>2501.9953071004629</v>
       </c>
@@ -682,7 +680,7 @@
         <v>2027</v>
       </c>
       <c r="C5" s="5">
-        <v>3660.143747464982</v>
+        <v>3669.0190784096339</v>
       </c>
       <c r="D5" s="5">
         <v>1008.0047307031887</v>
@@ -693,13 +691,11 @@
       <c r="F5" s="5">
         <v>7900.2130668713089</v>
       </c>
-      <c r="G5" s="5">
-        <v>2259.1950231492797</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5">
-        <v>1625.0577269054047</v>
-      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5">
+        <v>571.86102506292889</v>
+      </c>
+      <c r="I5" s="5"/>
       <c r="J5" s="5">
         <v>3835.6244504194347</v>
       </c>
@@ -725,7 +721,7 @@
         <v>2028</v>
       </c>
       <c r="C6" s="5">
-        <v>3582.3763563740481</v>
+        <v>3581.2295635002265</v>
       </c>
       <c r="D6" s="5">
         <v>-383.33124786745475</v>
@@ -736,13 +732,11 @@
       <c r="F6" s="5">
         <v>8970.6623737203936</v>
       </c>
-      <c r="G6" s="5">
-        <v>2478.0978770114771</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5">
-        <v>1512.8503706123583</v>
-      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5">
+        <v>5741.6580904322391</v>
+      </c>
+      <c r="I6" s="5"/>
       <c r="J6" s="5">
         <v>3285.1223048517027</v>
       </c>
@@ -768,7 +762,7 @@
         <v>2029</v>
       </c>
       <c r="C7" s="5">
-        <v>4425.1607962207636</v>
+        <v>4502.91993499617</v>
       </c>
       <c r="D7" s="5">
         <v>2230.8222624931559</v>
@@ -779,13 +773,11 @@
       <c r="F7" s="5">
         <v>9237.6405361497691</v>
       </c>
-      <c r="G7" s="5">
-        <v>3127.6169503912374</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5">
-        <v>1364.3379496901132</v>
-      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5">
+        <v>4500.4066499354121</v>
+      </c>
+      <c r="I7" s="5"/>
       <c r="J7" s="5">
         <v>3937.1846059278014</v>
       </c>
@@ -811,7 +803,7 @@
         <v>2030</v>
       </c>
       <c r="C8" s="5">
-        <v>4210.439705807612</v>
+        <v>4361.5850186626867</v>
       </c>
       <c r="D8" s="5">
         <v>5320.9952403656134</v>
@@ -822,13 +814,11 @@
       <c r="F8" s="5">
         <v>10839.835620002665</v>
       </c>
-      <c r="G8" s="5">
-        <v>3135.4157475244697</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5">
-        <v>904.45875123107317</v>
-      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5">
+        <v>11261.449314901685</v>
+      </c>
+      <c r="I8" s="5"/>
       <c r="J8" s="5">
         <v>4170.6304024117471</v>
       </c>
@@ -854,7 +844,7 @@
         <v>2031</v>
       </c>
       <c r="C9" s="5">
-        <v>5058.9868636215051</v>
+        <v>5319.7080113019883</v>
       </c>
       <c r="D9" s="5">
         <v>5838.2169035851375</v>
@@ -865,13 +855,11 @@
       <c r="F9" s="5">
         <v>10211.313108230523</v>
       </c>
-      <c r="G9" s="5">
-        <v>5091.8442177925972</v>
-      </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5">
-        <v>1442.8759435865741</v>
-      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5">
+        <v>7387.0977385815077</v>
+      </c>
+      <c r="I9" s="5"/>
       <c r="J9" s="5">
         <v>4248.1864762641917</v>
       </c>
@@ -897,7 +885,7 @@
         <v>2032</v>
       </c>
       <c r="C10" s="5">
-        <v>5490.5886142238132</v>
+        <v>5795.8635594562811</v>
       </c>
       <c r="D10" s="5">
         <v>7470.658368937854</v>
@@ -908,13 +896,11 @@
       <c r="F10" s="5">
         <v>9987.3934409373414</v>
       </c>
-      <c r="G10" s="5">
-        <v>5098.8551820805624</v>
-      </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5">
-        <v>1478.278136200965</v>
-      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5">
+        <v>9358.7473592724</v>
+      </c>
+      <c r="I10" s="5"/>
       <c r="J10" s="5">
         <v>4454.0089124215929</v>
       </c>
@@ -940,7 +926,7 @@
         <v>2033</v>
       </c>
       <c r="C11" s="5">
-        <v>5449.6911283321651</v>
+        <v>5762.5220376360421</v>
       </c>
       <c r="D11" s="5">
         <v>5493.0997048113531</v>
@@ -951,13 +937,11 @@
       <c r="F11" s="5">
         <v>9680.9944600591734</v>
       </c>
-      <c r="G11" s="5">
-        <v>5223.4525592457339</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5">
-        <v>1702.812375841015</v>
-      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5">
+        <v>7166.7354268685231</v>
+      </c>
+      <c r="I11" s="5"/>
       <c r="J11" s="5">
         <v>4278.6716997757094</v>
       </c>
@@ -983,7 +967,7 @@
         <v>2034</v>
       </c>
       <c r="C12" s="5">
-        <v>5465.2057201785474</v>
+        <v>5778.452112158544</v>
       </c>
       <c r="D12" s="5">
         <v>11308.504943659194</v>
@@ -994,13 +978,11 @@
       <c r="F12" s="5">
         <v>9921.497499168494</v>
       </c>
-      <c r="G12" s="5">
-        <v>5584.8625290540622</v>
-      </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5">
-        <v>1979.6073019892672</v>
-      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5">
+        <v>7253.5847988352061</v>
+      </c>
+      <c r="I12" s="5"/>
       <c r="J12" s="5">
         <v>4259.000194904238</v>
       </c>
@@ -1026,7 +1008,7 @@
         <v>2035</v>
       </c>
       <c r="C13" s="5">
-        <v>5657.9555381712644</v>
+        <v>5978.6514978773885</v>
       </c>
       <c r="D13" s="5">
         <v>11680.517848620657</v>
@@ -1037,13 +1019,11 @@
       <c r="F13" s="5">
         <v>6527.7649641655671</v>
       </c>
-      <c r="G13" s="5">
-        <v>5490.4819889390856</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5">
-        <v>1993.5461747859215</v>
-      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5">
+        <v>7081.5645139247781</v>
+      </c>
+      <c r="I13" s="5"/>
       <c r="J13" s="5">
         <v>4383.4562577475817</v>
       </c>
@@ -1072,7 +1052,7 @@
         <v>2036</v>
       </c>
       <c r="C14" s="5">
-        <v>5565.9368892212588</v>
+        <v>5892.6838143523755</v>
       </c>
       <c r="D14" s="5">
         <v>11587.516251420138</v>
@@ -1083,13 +1063,11 @@
       <c r="F14" s="5">
         <v>9674.569649226436</v>
       </c>
-      <c r="G14" s="5">
-        <v>5570.4881470965656</v>
-      </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5">
-        <v>1999.1896102157625</v>
-      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5">
+        <v>6692.9544613077132</v>
+      </c>
+      <c r="I14" s="5"/>
       <c r="J14" s="5">
         <v>3832.9880163038811</v>
       </c>
@@ -1118,7 +1096,7 @@
         <v>2037</v>
       </c>
       <c r="C15" s="5">
-        <v>5581.4196732150995</v>
+        <v>5914.5016849835538</v>
       </c>
       <c r="D15" s="5">
         <v>10348.675117827352</v>
@@ -1129,13 +1107,11 @@
       <c r="F15" s="5">
         <v>9501.6374868994753</v>
       </c>
-      <c r="G15" s="5">
-        <v>5430.9492258061327</v>
-      </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5">
-        <v>1469.3286433478743</v>
-      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5">
+        <v>6126.0097076854936</v>
+      </c>
+      <c r="I15" s="5"/>
       <c r="J15" s="5">
         <v>3913.2565172921413</v>
       </c>
@@ -1164,7 +1140,7 @@
         <v>2038</v>
       </c>
       <c r="C16" s="5">
-        <v>5667.3724990695691</v>
+        <v>6006.1810494023375</v>
       </c>
       <c r="D16" s="5">
         <v>9768.6833032279974</v>
@@ -1175,13 +1151,11 @@
       <c r="F16" s="5">
         <v>9477.7672293524847</v>
       </c>
-      <c r="G16" s="5">
-        <v>5281.6984417918602</v>
-      </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5">
-        <v>1508.0722156017994</v>
-      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5">
+        <v>5927.0993798750651</v>
+      </c>
+      <c r="I16" s="5"/>
       <c r="J16" s="5">
         <v>3937.7147867173735</v>
       </c>
@@ -1210,7 +1184,7 @@
         <v>2039</v>
       </c>
       <c r="C17" s="5">
-        <v>5714.844584718162</v>
+        <v>6059.8502777089043</v>
       </c>
       <c r="D17" s="5">
         <v>10155.942786401696</v>
@@ -1221,13 +1195,11 @@
       <c r="F17" s="5">
         <v>9451.957591022785</v>
       </c>
-      <c r="G17" s="5">
-        <v>5455.0497239954748</v>
-      </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5">
-        <v>1609.051536376933</v>
-      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5">
+        <v>4963.6730414739986</v>
+      </c>
+      <c r="I17" s="5"/>
       <c r="J17" s="5">
         <v>2101.0446766878317</v>
       </c>
@@ -1256,7 +1228,7 @@
         <v>2040</v>
       </c>
       <c r="C18" s="5">
-        <v>5646.4806655678176</v>
+        <v>5999.9258054264137</v>
       </c>
       <c r="D18" s="5">
         <v>10330.306705276818</v>
@@ -1267,13 +1239,11 @@
       <c r="F18" s="5">
         <v>9809.1114632965837</v>
       </c>
-      <c r="G18" s="5">
-        <v>5562.4537677373455</v>
-      </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5">
-        <v>905.55856109873594</v>
-      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5">
+        <v>7208.8400006301054</v>
+      </c>
+      <c r="I18" s="5"/>
       <c r="J18" s="5">
         <v>2935.3275547712306</v>
       </c>
@@ -1302,7 +1272,7 @@
         <v>2041</v>
       </c>
       <c r="C19" s="5">
-        <v>5314.7528189505028</v>
+        <v>5677.6161310753932</v>
       </c>
       <c r="D19" s="5">
         <v>9547.3412998822914</v>
@@ -1313,13 +1283,11 @@
       <c r="F19" s="5">
         <v>8177.7095148837079</v>
       </c>
-      <c r="G19" s="5">
-        <v>4547.2721925786218</v>
-      </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5">
-        <v>1571.163826467832</v>
-      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5">
+        <v>4294.8172899213159</v>
+      </c>
+      <c r="I19" s="5"/>
       <c r="J19" s="5">
         <v>2176.8108881056482</v>
       </c>
@@ -1348,7 +1316,7 @@
         <v>2042</v>
       </c>
       <c r="C20" s="5">
-        <v>7991.7263392091545</v>
+        <v>8360.2968485096317</v>
       </c>
       <c r="D20" s="5">
         <v>5116.222974985365</v>
@@ -1359,13 +1327,11 @@
       <c r="F20" s="5">
         <v>6902.4335581849218</v>
       </c>
-      <c r="G20" s="5">
-        <v>4591.0521644979535</v>
-      </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5">
-        <v>3429.6463359064046</v>
-      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5">
+        <v>4217.1059468134536</v>
+      </c>
+      <c r="I20" s="5"/>
       <c r="J20" s="5">
         <v>2023.8412444417288</v>
       </c>
@@ -1394,7 +1360,7 @@
         <v>2043</v>
       </c>
       <c r="C21" s="5">
-        <v>4418.7495968982048</v>
+        <v>4801.9342601853914</v>
       </c>
       <c r="D21" s="5">
         <v>5225.6606237213318</v>
@@ -1405,13 +1371,11 @@
       <c r="F21" s="5">
         <v>6264.1358442520304</v>
       </c>
-      <c r="G21" s="5">
-        <v>4343.9829427370814</v>
-      </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5">
-        <v>3575.9025766681743</v>
-      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5">
+        <v>2877.6075581734044</v>
+      </c>
+      <c r="I21" s="5"/>
       <c r="J21" s="5">
         <v>1870.1047578422101</v>
       </c>
@@ -1440,7 +1404,7 @@
         <v>2044</v>
       </c>
       <c r="C22" s="5">
-        <v>4302.338533913191</v>
+        <v>4696.1977097082081</v>
       </c>
       <c r="D22" s="5">
         <v>7421.6683063923683</v>
@@ -1451,13 +1415,11 @@
       <c r="F22" s="5">
         <v>7208.5854147848531</v>
       </c>
-      <c r="G22" s="5">
-        <v>4864.1456318902165</v>
-      </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5">
-        <v>208.43109107741782</v>
-      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5">
+        <v>212.82375022969396</v>
+      </c>
+      <c r="I22" s="5"/>
       <c r="J22" s="5">
         <v>1961.2355100722823</v>
       </c>
@@ -1486,7 +1448,7 @@
         <v>2045</v>
       </c>
       <c r="C23" s="5">
-        <v>-5318.5893187219672</v>
+        <v>-5047.4529143256914</v>
       </c>
       <c r="D23" s="5">
         <v>8047.2674890790931</v>
@@ -1497,13 +1459,11 @@
       <c r="F23" s="5">
         <v>7251.4632082702119</v>
       </c>
-      <c r="G23" s="5">
-        <v>4826.8320156433474</v>
-      </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5">
-        <v>625.32963005381805</v>
-      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5">
+        <v>-745.09693808956933</v>
+      </c>
+      <c r="I23" s="5"/>
       <c r="J23" s="5">
         <v>807.89927763605942</v>
       </c>
@@ -1532,7 +1492,7 @@
         <v>2046</v>
       </c>
       <c r="C24" s="5">
-        <v>20472.232012192413</v>
+        <v>20575.891618853337</v>
       </c>
       <c r="D24" s="5">
         <v>17133.14369506764</v>
@@ -1543,13 +1503,11 @@
       <c r="F24" s="5">
         <v>8154.2210641793599</v>
       </c>
-      <c r="G24" s="5">
-        <v>4107.4633820636591</v>
-      </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5">
-        <v>882.36437232330456</v>
-      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5">
+        <v>-1311.4975429657518</v>
+      </c>
+      <c r="I24" s="5"/>
       <c r="J24" s="5">
         <v>854.24973682712641</v>
       </c>
@@ -1578,7 +1536,7 @@
         <v>2047</v>
       </c>
       <c r="C25" s="5">
-        <v>1150.1898105245825</v>
+        <v>1214.2424272316221</v>
       </c>
       <c r="D25" s="5">
         <v>6640.3369228731744</v>
@@ -1589,13 +1547,11 @@
       <c r="F25" s="5">
         <v>8198.0874546577325</v>
       </c>
-      <c r="G25" s="5">
-        <v>4204.7632074703888</v>
-      </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5">
-        <v>5717.7724254876202</v>
-      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5">
+        <v>-1288.8289541279607</v>
+      </c>
+      <c r="I25" s="5"/>
       <c r="J25" s="5">
         <v>873.16574575509287</v>
       </c>
@@ -1624,7 +1580,7 @@
         <v>2048</v>
       </c>
       <c r="C26" s="5">
-        <v>1000.2915388927777</v>
+        <v>1062.282033869428</v>
       </c>
       <c r="D26" s="5">
         <v>-36256.629550042744</v>
@@ -1635,13 +1591,11 @@
       <c r="F26" s="5">
         <v>8278.9794027489297</v>
       </c>
-      <c r="G26" s="5">
-        <v>3929.1449403481429</v>
-      </c>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5">
-        <v>1263.9425839796477</v>
-      </c>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5">
+        <v>-1045.1796218484294</v>
+      </c>
+      <c r="I26" s="5"/>
       <c r="J26" s="5">
         <v>790.38698278973141</v>
       </c>
@@ -1670,7 +1624,7 @@
         <v>2049</v>
       </c>
       <c r="C27" s="5">
-        <v>1013.2949582724123</v>
+        <v>1075.2996160344092</v>
       </c>
       <c r="D27" s="5">
         <v>58720.223253545359</v>
@@ -1681,13 +1635,11 @@
       <c r="F27" s="5">
         <v>8351.1674389202817</v>
       </c>
-      <c r="G27" s="5">
-        <v>4359.9855593499242</v>
-      </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5">
-        <v>21.722954410910749</v>
-      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5">
+        <v>-1619.4528413006619</v>
+      </c>
+      <c r="I27" s="5"/>
       <c r="J27" s="5">
         <v>-116.07390559453955</v>
       </c>
@@ -1716,7 +1668,7 @@
         <v>2050</v>
       </c>
       <c r="C28" s="5">
-        <v>982.63393501217752</v>
+        <v>1037.6105067584497</v>
       </c>
       <c r="D28" s="5">
         <v>1953.156109231425</v>
@@ -1727,13 +1679,11 @@
       <c r="F28" s="5">
         <v>8321.4072834855524</v>
       </c>
-      <c r="G28" s="5">
-        <v>5226.3542632588751</v>
-      </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5">
-        <v>31.607676579629818</v>
-      </c>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5">
+        <v>-1619.5320044668408</v>
+      </c>
+      <c r="I28" s="5"/>
       <c r="J28" s="5">
         <v>-227.95215347026419</v>
       </c>
@@ -1762,7 +1712,7 @@
         <v>2051</v>
       </c>
       <c r="C29" s="5">
-        <v>949.36586851326774</v>
+        <v>997.19595060247661</v>
       </c>
       <c r="D29" s="5">
         <v>2076.2237893806973</v>
@@ -1773,13 +1723,11 @@
       <c r="F29" s="5">
         <v>9144.8197090018821</v>
       </c>
-      <c r="G29" s="5">
-        <v>5055.0627512252313</v>
-      </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5">
-        <v>565.45374305641292</v>
-      </c>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5">
+        <v>-1548.3264858205901</v>
+      </c>
+      <c r="I29" s="5"/>
       <c r="J29" s="5">
         <v>-184.46003839554967</v>
       </c>
@@ -1808,7 +1756,7 @@
         <v>2052</v>
       </c>
       <c r="C30" s="5">
-        <v>1227.873670728768</v>
+        <v>1275.691675692382</v>
       </c>
       <c r="D30" s="5">
         <v>5663.0097529148252</v>
@@ -1819,13 +1767,11 @@
       <c r="F30" s="5">
         <v>9162.796070732622</v>
       </c>
-      <c r="G30" s="5">
-        <v>5039.7898278747607</v>
-      </c>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5">
-        <v>-2028.5808695841597</v>
-      </c>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5">
+        <v>-17113.236494752273</v>
+      </c>
+      <c r="I30" s="5"/>
       <c r="J30" s="5">
         <v>-106.31302552011442</v>
       </c>
@@ -1854,7 +1800,7 @@
         <v>2053</v>
       </c>
       <c r="C31" s="5">
-        <v>826.4587927119029</v>
+        <v>874.40687200636512</v>
       </c>
       <c r="D31" s="5">
         <v>2025.9664180611614</v>
@@ -1865,13 +1811,9 @@
       <c r="F31" s="5">
         <v>9216.2516001340518</v>
       </c>
-      <c r="G31" s="5">
-        <v>4744.7092284408018</v>
-      </c>
+      <c r="G31" s="5"/>
       <c r="H31" s="5"/>
-      <c r="I31" s="5">
-        <v>-45.921960791611475</v>
-      </c>
+      <c r="I31" s="5"/>
       <c r="J31" s="5">
         <v>13.935187786349861</v>
       </c>
@@ -1900,7 +1842,7 @@
         <v>2054</v>
       </c>
       <c r="C32" s="5">
-        <v>236.94676705743296</v>
+        <v>260.03440681628842</v>
       </c>
       <c r="D32" s="5">
         <v>1919.8539728117053</v>
@@ -1909,13 +1851,9 @@
       <c r="F32" s="5">
         <v>9262.1506561333863</v>
       </c>
-      <c r="G32" s="5">
-        <v>-14671.572646668461</v>
-      </c>
+      <c r="G32" s="5"/>
       <c r="H32" s="5"/>
-      <c r="I32" s="5">
-        <v>-37.010932626242912</v>
-      </c>
+      <c r="I32" s="5"/>
       <c r="J32" s="5">
         <v>81.213714187589304</v>
       </c>
@@ -1944,7 +1882,7 @@
         <v>2055</v>
       </c>
       <c r="C33" s="5">
-        <v>-3197.1599030428097</v>
+        <v>-3184.8227946917996</v>
       </c>
       <c r="D33" s="5">
         <v>1809.1392026497824</v>
@@ -1953,13 +1891,9 @@
       <c r="F33" s="5">
         <v>9211.7283853004719</v>
       </c>
-      <c r="G33" s="5">
-        <v>55386.705890640995</v>
-      </c>
+      <c r="G33" s="5"/>
       <c r="H33" s="5"/>
-      <c r="I33" s="5">
-        <v>-30.127705403040821</v>
-      </c>
+      <c r="I33" s="5"/>
       <c r="J33" s="5">
         <v>-210.5734693421868</v>
       </c>
@@ -1997,9 +1931,7 @@
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
-      <c r="I34" s="5">
-        <v>-50.937750239084195</v>
-      </c>
+      <c r="I34" s="5"/>
       <c r="J34" s="5">
         <v>-583.55332889163435</v>
       </c>
@@ -2037,9 +1969,7 @@
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
-      <c r="I35" s="5">
-        <v>-117.11967923122944</v>
-      </c>
+      <c r="I35" s="5"/>
       <c r="J35" s="5">
         <v>-978.1043834942775</v>
       </c>
@@ -2077,9 +2007,7 @@
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
-      <c r="I36" s="5">
-        <v>-1499.9268304457303</v>
-      </c>
+      <c r="I36" s="5"/>
       <c r="J36" s="5">
         <v>-931.82308742781004</v>
       </c>
@@ -2294,6 +2222,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020E4BAF79DB213408BB296F3F8F32329" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9679123e7a51fb6c2fee49c985862cfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457" xmlns:ns3="f0bab05a-e9c1-4e32-93e9-8363aec9c620" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ddaff962f7439efafa6fc254a8996caa" ns2:_="" ns3:_="">
     <xsd:import namespace="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
@@ -2528,17 +2467,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
   <ds:schemaRefs>
@@ -2548,6 +2476,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47140DD7-5C12-4BA5-9C24-A1CF0564C7A2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
+    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2564,15 +2503,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47140DD7-5C12-4BA5-9C24-A1CF0564C7A2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
-    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/irrdash3.xlsx
+++ b/irrdash3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.russo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D3E71CD-6554-4BA8-AE7C-5ACE284D0AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED15E5E3-5573-4AB7-B34C-EB2BE8E437F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -639,7 +639,7 @@
         <v>2026</v>
       </c>
       <c r="C4" s="5">
-        <v>3354.9604906857189</v>
+        <v>2745.4364798654174</v>
       </c>
       <c r="D4" s="5">
         <v>2346.2961342640269</v>
@@ -647,16 +647,14 @@
       <c r="E4" s="5">
         <v>1423.5911688211188</v>
       </c>
-      <c r="F4" s="5">
-        <v>6605.1316597436398</v>
-      </c>
+      <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5">
-        <v>777.22850688213123</v>
+        <v>-8.7620158507064616</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5">
-        <v>2501.9953071004629</v>
+        <v>2529.7503686473783</v>
       </c>
       <c r="K4" s="5">
         <v>954.45860804386211</v>
@@ -667,9 +665,7 @@
       <c r="M4" s="5">
         <v>1226.6329817372125</v>
       </c>
-      <c r="N4" s="5">
-        <v>12287.951266142702</v>
-      </c>
+      <c r="N4" s="5"/>
       <c r="O4" s="5">
         <v>18511.406301685623</v>
       </c>
@@ -680,7 +676,7 @@
         <v>2027</v>
       </c>
       <c r="C5" s="5">
-        <v>3669.0190784096339</v>
+        <v>5030.9414324565514</v>
       </c>
       <c r="D5" s="5">
         <v>1008.0047307031887</v>
@@ -688,16 +684,14 @@
       <c r="E5" s="5">
         <v>836.48604610360985</v>
       </c>
-      <c r="F5" s="5">
-        <v>7900.2130668713089</v>
-      </c>
+      <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
-        <v>571.86102506292889</v>
+        <v>952.98742767157978</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5">
-        <v>3835.6244504194347</v>
+        <v>4030.7434720901692</v>
       </c>
       <c r="K5" s="5">
         <v>1323.0224151276375</v>
@@ -708,9 +702,7 @@
       <c r="M5" s="5">
         <v>1314.4750719842391</v>
       </c>
-      <c r="N5" s="5">
-        <v>10691.467761164782</v>
-      </c>
+      <c r="N5" s="5"/>
       <c r="O5" s="5">
         <v>22879.286074147032</v>
       </c>
@@ -721,7 +713,7 @@
         <v>2028</v>
       </c>
       <c r="C6" s="5">
-        <v>3581.2295635002265</v>
+        <v>4878.854572172454</v>
       </c>
       <c r="D6" s="5">
         <v>-383.33124786745475</v>
@@ -729,16 +721,14 @@
       <c r="E6" s="5">
         <v>1886.5332002018404</v>
       </c>
-      <c r="F6" s="5">
-        <v>8970.6623737203936</v>
-      </c>
+      <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
-        <v>5741.6580904322391</v>
+        <v>6589.9422482750315</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5">
-        <v>3285.1223048517027</v>
+        <v>3566.5249518951969</v>
       </c>
       <c r="K6" s="5">
         <v>1507.4723309960461</v>
@@ -749,9 +739,7 @@
       <c r="M6" s="5">
         <v>1582.1842275077693</v>
       </c>
-      <c r="N6" s="5">
-        <v>9953.2408585075154</v>
-      </c>
+      <c r="N6" s="5"/>
       <c r="O6" s="5">
         <v>21037.072244304934</v>
       </c>
@@ -762,7 +750,7 @@
         <v>2029</v>
       </c>
       <c r="C7" s="5">
-        <v>4502.91993499617</v>
+        <v>4847.5209112119855</v>
       </c>
       <c r="D7" s="5">
         <v>2230.8222624931559</v>
@@ -770,16 +758,14 @@
       <c r="E7" s="5">
         <v>2728.8526153584262</v>
       </c>
-      <c r="F7" s="5">
-        <v>9237.6405361497691</v>
-      </c>
+      <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
-        <v>4500.4066499354121</v>
+        <v>5536.1237456745603</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5">
-        <v>3937.1846059278014</v>
+        <v>4588.6153429819633</v>
       </c>
       <c r="K7" s="5">
         <v>1635.8695434730157</v>
@@ -790,9 +776,7 @@
       <c r="M7" s="5">
         <v>1741.7854333559026</v>
       </c>
-      <c r="N7" s="5">
-        <v>8976.1581776070689</v>
-      </c>
+      <c r="N7" s="5"/>
       <c r="O7" s="5">
         <v>14257.130957783082</v>
       </c>
@@ -803,7 +787,7 @@
         <v>2030</v>
       </c>
       <c r="C8" s="5">
-        <v>4361.5850186626867</v>
+        <v>5160.437064035852</v>
       </c>
       <c r="D8" s="5">
         <v>5320.9952403656134</v>
@@ -811,16 +795,14 @@
       <c r="E8" s="5">
         <v>1996.046006674206</v>
       </c>
-      <c r="F8" s="5">
-        <v>10839.835620002665</v>
-      </c>
+      <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
-        <v>11261.449314901685</v>
+        <v>12017.286584211188</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5">
-        <v>4170.6304024117471</v>
+        <v>4875.0359796024486</v>
       </c>
       <c r="K8" s="5">
         <v>1746.0218707119739</v>
@@ -831,9 +813,7 @@
       <c r="M8" s="5">
         <v>1892.8027068433896</v>
       </c>
-      <c r="N8" s="5">
-        <v>5950.552660369136</v>
-      </c>
+      <c r="N8" s="5"/>
       <c r="O8" s="5">
         <v>14572.640722376331</v>
       </c>
@@ -844,7 +824,7 @@
         <v>2031</v>
       </c>
       <c r="C9" s="5">
-        <v>5319.7080113019883</v>
+        <v>6196.4049493969596</v>
       </c>
       <c r="D9" s="5">
         <v>5838.2169035851375</v>
@@ -852,16 +832,14 @@
       <c r="E9" s="5">
         <v>3040.4333366384258</v>
       </c>
-      <c r="F9" s="5">
-        <v>10211.313108230523</v>
-      </c>
+      <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
-        <v>7387.0977385815077</v>
+        <v>8473.7455168781198</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5">
-        <v>4248.1864762641917</v>
+        <v>4761.4819818872274</v>
       </c>
       <c r="K9" s="5">
         <v>1824.9420592681549</v>
@@ -872,9 +850,7 @@
       <c r="M9" s="5">
         <v>1978.3573891927106</v>
       </c>
-      <c r="N9" s="5">
-        <v>9492.8699324378231</v>
-      </c>
+      <c r="N9" s="5"/>
       <c r="O9" s="5">
         <v>14256.83359063529</v>
       </c>
@@ -885,7 +861,7 @@
         <v>2032</v>
       </c>
       <c r="C10" s="5">
-        <v>5795.8635594562811</v>
+        <v>6699.1790561707985</v>
       </c>
       <c r="D10" s="5">
         <v>7470.658368937854</v>
@@ -893,16 +869,14 @@
       <c r="E10" s="5">
         <v>3079.6282281473705</v>
       </c>
-      <c r="F10" s="5">
-        <v>9987.3934409373414</v>
-      </c>
+      <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
-        <v>9358.7473592724</v>
+        <v>11404.257473885451</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5">
-        <v>4454.0089124215929</v>
+        <v>4924.3243098120347</v>
       </c>
       <c r="K10" s="5">
         <v>1907.4294403470753</v>
@@ -913,9 +887,7 @@
       <c r="M10" s="5">
         <v>2067.7791431842211</v>
       </c>
-      <c r="N10" s="5">
-        <v>9725.7855973675159</v>
-      </c>
+      <c r="N10" s="5"/>
       <c r="O10" s="5">
         <v>14916.449828221348</v>
       </c>
@@ -926,7 +898,7 @@
         <v>2033</v>
       </c>
       <c r="C11" s="5">
-        <v>5762.5220376360421</v>
+        <v>6773.3605098858025</v>
       </c>
       <c r="D11" s="5">
         <v>5493.0997048113531</v>
@@ -934,16 +906,14 @@
       <c r="E11" s="5">
         <v>3365.750967532942</v>
       </c>
-      <c r="F11" s="5">
-        <v>9680.9944600591734</v>
-      </c>
+      <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
-        <v>7166.7354268685231</v>
+        <v>9338.3280772234048</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5">
-        <v>4278.6716997757094</v>
+        <v>4605.2258897465108</v>
       </c>
       <c r="K11" s="5">
         <v>1993.6452510507629</v>
@@ -954,9 +924,7 @@
       <c r="M11" s="5">
         <v>2161.2427604561476</v>
       </c>
-      <c r="N11" s="5">
-        <v>11203.02578683494</v>
-      </c>
+      <c r="N11" s="5"/>
       <c r="O11" s="5">
         <v>14802.022900230375</v>
       </c>
@@ -967,7 +935,7 @@
         <v>2034</v>
       </c>
       <c r="C12" s="5">
-        <v>5778.452112158544</v>
+        <v>6876.5340588649724</v>
       </c>
       <c r="D12" s="5">
         <v>11308.504943659194</v>
@@ -975,16 +943,14 @@
       <c r="E12" s="5">
         <v>3998.2297037974399</v>
       </c>
-      <c r="F12" s="5">
-        <v>9921.497499168494</v>
-      </c>
+      <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
-        <v>7253.5847988352061</v>
+        <v>9426.7694638763442</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5">
-        <v>4259.000194904238</v>
+        <v>4576.5670350656956</v>
       </c>
       <c r="K12" s="5">
         <v>2083.758016398257</v>
@@ -995,9 +961,7 @@
       <c r="M12" s="5">
         <v>2258.9309332287653</v>
       </c>
-      <c r="N12" s="5">
-        <v>13024.095881989959</v>
-      </c>
+      <c r="N12" s="5"/>
       <c r="O12" s="5">
         <v>14927.501604703333</v>
       </c>
@@ -1008,7 +972,7 @@
         <v>2035</v>
       </c>
       <c r="C13" s="5">
-        <v>5978.6514978773885</v>
+        <v>7138.8046805764006</v>
       </c>
       <c r="D13" s="5">
         <v>11680.517848620657</v>
@@ -1016,16 +980,14 @@
       <c r="E13" s="5">
         <v>3357.9892161586899</v>
       </c>
-      <c r="F13" s="5">
-        <v>6527.7649641655671</v>
-      </c>
+      <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5">
-        <v>7081.5645139247781</v>
+        <v>9290.320997467421</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5">
-        <v>4383.4562577475817</v>
+        <v>4690.9302019998759</v>
       </c>
       <c r="K13" s="5">
         <f>K12*1.045</f>
@@ -1039,9 +1001,7 @@
         <f>M12*1.045</f>
         <v>2360.5828252240594</v>
       </c>
-      <c r="N13" s="5">
-        <v>13115.801552911693</v>
-      </c>
+      <c r="N13" s="5"/>
       <c r="O13" s="5">
         <v>8966.776435412432</v>
       </c>
@@ -1052,7 +1012,7 @@
         <v>2036</v>
       </c>
       <c r="C14" s="5">
-        <v>5892.6838143523755</v>
+        <v>7109.0430282295492</v>
       </c>
       <c r="D14" s="5">
         <v>11587.516251420138</v>
@@ -1060,16 +1020,14 @@
       <c r="E14" s="5">
         <v>3890.7284841014853</v>
       </c>
-      <c r="F14" s="5">
-        <v>9674.569649226436</v>
-      </c>
+      <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
-        <v>6692.9544613077132</v>
+        <v>8673.6495661046774</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5">
-        <v>3832.9880163038811</v>
+        <v>4015.893017098268</v>
       </c>
       <c r="K14" s="5">
         <f t="shared" ref="K14:M29" si="1">K13*1.045</f>
@@ -1083,9 +1041,7 @@
         <f t="shared" si="1"/>
         <v>2466.8090523591418</v>
       </c>
-      <c r="N14" s="5">
-        <v>13152.930454218638</v>
-      </c>
+      <c r="N14" s="5"/>
       <c r="O14" s="5">
         <v>9170.2795180922367</v>
       </c>
@@ -1096,7 +1052,7 @@
         <v>2037</v>
       </c>
       <c r="C15" s="5">
-        <v>5914.5016849835538</v>
+        <v>7185.1894287338318</v>
       </c>
       <c r="D15" s="5">
         <v>10348.675117827352</v>
@@ -1104,16 +1060,14 @@
       <c r="E15" s="5">
         <v>3795.421343208634</v>
       </c>
-      <c r="F15" s="5">
-        <v>9501.6374868994753</v>
-      </c>
+      <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
-        <v>6126.0097076854936</v>
+        <v>8188.6870790363791</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5">
-        <v>3913.2565172921413</v>
+        <v>4120.0479243237787</v>
       </c>
       <c r="K15" s="5">
         <f t="shared" si="1"/>
@@ -1127,9 +1081,7 @@
         <f t="shared" si="1"/>
         <v>2577.8154597153029</v>
       </c>
-      <c r="N15" s="5">
-        <v>9666.905710989693</v>
-      </c>
+      <c r="N15" s="5"/>
       <c r="O15" s="5">
         <v>9901.0095168224398</v>
       </c>
@@ -1140,7 +1092,7 @@
         <v>2038</v>
       </c>
       <c r="C16" s="5">
-        <v>6006.1810494023375</v>
+        <v>7365.6208094844114</v>
       </c>
       <c r="D16" s="5">
         <v>9768.6833032279974</v>
@@ -1148,16 +1100,14 @@
       <c r="E16" s="5">
         <v>4241.1276645324469</v>
       </c>
-      <c r="F16" s="5">
-        <v>9477.7672293524847</v>
-      </c>
+      <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
-        <v>5927.0993798750651</v>
+        <v>8004.3987166707338</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5">
-        <v>3937.7147867173735</v>
+        <v>4142.8664773663277</v>
       </c>
       <c r="K16" s="5">
         <f t="shared" si="1"/>
@@ -1171,9 +1121,7 @@
         <f t="shared" si="1"/>
         <v>2693.8171554024916</v>
       </c>
-      <c r="N16" s="5">
-        <v>9921.8047504804363</v>
-      </c>
+      <c r="N16" s="5"/>
       <c r="O16" s="5">
         <v>16924.708304675674</v>
       </c>
@@ -1184,7 +1132,7 @@
         <v>2039</v>
       </c>
       <c r="C17" s="5">
-        <v>6059.8502777089043</v>
+        <v>7508.1630455113282</v>
       </c>
       <c r="D17" s="5">
         <v>10155.942786401696</v>
@@ -1192,16 +1140,14 @@
       <c r="E17" s="5">
         <v>4700.1076438236432</v>
       </c>
-      <c r="F17" s="5">
-        <v>9451.957591022785</v>
-      </c>
+      <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
-        <v>4963.6730414739986</v>
+        <v>7114.7800115611963</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5">
-        <v>2101.0446766878317</v>
+        <v>2338.3601542388742</v>
       </c>
       <c r="K17" s="5">
         <f t="shared" si="1"/>
@@ -1215,9 +1161,7 @@
         <f t="shared" si="1"/>
         <v>2815.0389273956034</v>
       </c>
-      <c r="N17" s="5">
-        <v>10586.160935948119</v>
-      </c>
+      <c r="N17" s="5"/>
       <c r="O17" s="5">
         <v>18304.907510996669</v>
       </c>
@@ -1228,7 +1172,7 @@
         <v>2040</v>
       </c>
       <c r="C18" s="5">
-        <v>5999.9258054264137</v>
+        <v>7491.1459400575186</v>
       </c>
       <c r="D18" s="5">
         <v>10330.306705276818</v>
@@ -1236,16 +1180,14 @@
       <c r="E18" s="5">
         <v>4448.8476307615656</v>
       </c>
-      <c r="F18" s="5">
-        <v>9809.1114632965837</v>
-      </c>
+      <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
-        <v>7208.8400006301054</v>
+        <v>8959.0426799030829</v>
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5">
-        <v>2935.3275547712306</v>
+        <v>3377.490981355998</v>
       </c>
       <c r="K18" s="5">
         <f t="shared" si="1"/>
@@ -1259,9 +1201,7 @@
         <f t="shared" si="1"/>
         <v>2941.7156791284056</v>
       </c>
-      <c r="N18" s="5">
-        <v>5957.7884536267202</v>
-      </c>
+      <c r="N18" s="5"/>
       <c r="O18" s="5">
         <v>19338.066657106887</v>
       </c>
@@ -1272,7 +1212,7 @@
         <v>2041</v>
       </c>
       <c r="C19" s="5">
-        <v>5677.6161310753932</v>
+        <v>6692.2296027473712</v>
       </c>
       <c r="D19" s="5">
         <v>9547.3412998822914</v>
@@ -1280,16 +1220,14 @@
       <c r="E19" s="5">
         <v>4404.6638333651717</v>
       </c>
-      <c r="F19" s="5">
-        <v>8177.7095148837079</v>
-      </c>
+      <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
-        <v>4294.8172899213159</v>
+        <v>5706.5892170742209</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5">
-        <v>2176.8108881056482</v>
+        <v>2678.6739276184658</v>
       </c>
       <c r="K19" s="5">
         <f t="shared" si="1"/>
@@ -1303,9 +1241,7 @@
         <f t="shared" si="1"/>
         <v>3074.0928846891834</v>
       </c>
-      <c r="N19" s="5">
-        <v>10336.892726991075</v>
-      </c>
+      <c r="N19" s="5"/>
       <c r="O19" s="5">
         <v>20929.557974011255</v>
       </c>
@@ -1316,7 +1252,7 @@
         <v>2042</v>
       </c>
       <c r="C20" s="5">
-        <v>8360.2968485096317</v>
+        <v>10022.354780335389</v>
       </c>
       <c r="D20" s="5">
         <v>5116.222974985365</v>
@@ -1324,16 +1260,14 @@
       <c r="E20" s="5">
         <v>4322.8251616964926</v>
       </c>
-      <c r="F20" s="5">
-        <v>6902.4335581849218</v>
-      </c>
+      <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5">
-        <v>4217.1059468134536</v>
+        <v>5791.5387040282367</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5">
-        <v>2023.8412444417288</v>
+        <v>2584.6922920529951</v>
       </c>
       <c r="K20" s="5">
         <f t="shared" si="1"/>
@@ -1347,9 +1281,7 @@
         <f t="shared" si="1"/>
         <v>3212.4270645001966</v>
       </c>
-      <c r="N20" s="5">
-        <v>22564.092724488615</v>
-      </c>
+      <c r="N20" s="5"/>
       <c r="O20" s="5">
         <v>28513.605545167349</v>
       </c>
@@ -1360,7 +1292,7 @@
         <v>2043</v>
       </c>
       <c r="C21" s="5">
-        <v>4801.9342601853914</v>
+        <v>5630.0233805802036</v>
       </c>
       <c r="D21" s="5">
         <v>5225.6606237213318</v>
@@ -1368,16 +1300,14 @@
       <c r="E21" s="5">
         <v>4704.9869228474563</v>
       </c>
-      <c r="F21" s="5">
-        <v>6264.1358442520304</v>
-      </c>
+      <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
-        <v>2877.6075581734044</v>
+        <v>3723.3268802003786</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5">
-        <v>1870.1047578422101</v>
+        <v>2520.1933975248608</v>
       </c>
       <c r="K21" s="5">
         <f t="shared" si="1"/>
@@ -1391,9 +1321,7 @@
         <f t="shared" si="1"/>
         <v>3356.986282402705</v>
       </c>
-      <c r="N21" s="5">
-        <v>23526.331700424169</v>
-      </c>
+      <c r="N21" s="5"/>
       <c r="O21" s="5">
         <v>19008.491823315748</v>
       </c>
@@ -1404,7 +1332,7 @@
         <v>2044</v>
       </c>
       <c r="C22" s="5">
-        <v>4696.1977097082081</v>
+        <v>5640.800647683538</v>
       </c>
       <c r="D22" s="5">
         <v>7421.6683063923683</v>
@@ -1412,16 +1340,14 @@
       <c r="E22" s="5">
         <v>5466.3907696940523</v>
       </c>
-      <c r="F22" s="5">
-        <v>7208.5854147848531</v>
-      </c>
+      <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5">
-        <v>212.82375022969396</v>
+        <v>2227.0346985504361</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5">
-        <v>1961.2355100722823</v>
+        <v>2617.1822257632862</v>
       </c>
       <c r="K22" s="5">
         <f t="shared" si="1"/>
@@ -1435,9 +1361,7 @@
         <f t="shared" si="1"/>
         <v>3508.0506651108267</v>
       </c>
-      <c r="N22" s="5">
-        <v>1371.2954646369503</v>
-      </c>
+      <c r="N22" s="5"/>
       <c r="O22" s="5">
         <v>19847.81212405007</v>
       </c>
@@ -1448,7 +1372,7 @@
         <v>2045</v>
       </c>
       <c r="C23" s="5">
-        <v>-5047.4529143256914</v>
+        <v>-4470.0060412833718</v>
       </c>
       <c r="D23" s="5">
         <v>8047.2674890790931</v>
@@ -1456,16 +1380,14 @@
       <c r="E23" s="5">
         <v>6800.1708681005994</v>
       </c>
-      <c r="F23" s="5">
-        <v>7251.4632082702119</v>
-      </c>
+      <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
-        <v>-745.09693808956933</v>
+        <v>661.03155598403737</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5">
-        <v>807.89927763605942</v>
+        <v>1542.3953309498245</v>
       </c>
       <c r="K23" s="5">
         <f t="shared" si="1"/>
@@ -1479,9 +1401,7 @@
         <f t="shared" si="1"/>
         <v>3665.9129450408136</v>
       </c>
-      <c r="N23" s="5">
-        <v>4114.1255902047551</v>
-      </c>
+      <c r="N23" s="5"/>
       <c r="O23" s="5">
         <v>20539.534716877293</v>
       </c>
@@ -1492,7 +1412,7 @@
         <v>2046</v>
       </c>
       <c r="C24" s="5">
-        <v>20575.891618853337</v>
+        <v>22223.170163740746</v>
       </c>
       <c r="D24" s="5">
         <v>17133.14369506764</v>
@@ -1500,16 +1420,14 @@
       <c r="E24" s="5">
         <v>4836.6248297612428</v>
       </c>
-      <c r="F24" s="5">
-        <v>8154.2210641793599</v>
-      </c>
+      <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
-        <v>-1311.4975429657518</v>
+        <v>-649.48826947455473</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5">
-        <v>854.24973682712641</v>
+        <v>1545.2662538634931</v>
       </c>
       <c r="K24" s="5">
         <f t="shared" si="1"/>
@@ -1523,9 +1441,7 @@
         <f t="shared" si="1"/>
         <v>3830.8790275676502</v>
       </c>
-      <c r="N24" s="5">
-        <v>5805.1908459028873</v>
-      </c>
+      <c r="N24" s="5"/>
       <c r="O24" s="5">
         <v>20702.885848859736</v>
       </c>
@@ -1536,7 +1452,7 @@
         <v>2047</v>
       </c>
       <c r="C25" s="5">
-        <v>1214.2424272316221</v>
+        <v>1761.6618872329177</v>
       </c>
       <c r="D25" s="5">
         <v>6640.3369228731744</v>
@@ -1544,16 +1460,14 @@
       <c r="E25" s="5">
         <v>4570.7074782877553</v>
       </c>
-      <c r="F25" s="5">
-        <v>8198.0874546577325</v>
-      </c>
+      <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5">
-        <v>-1288.8289541279607</v>
+        <v>-758.26620108825864</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5">
-        <v>873.16574575509287</v>
+        <v>1512.2213829386369</v>
       </c>
       <c r="K25" s="5">
         <f t="shared" si="1"/>
@@ -1567,9 +1481,7 @@
         <f t="shared" si="1"/>
         <v>4003.2685838081943</v>
       </c>
-      <c r="N25" s="5">
-        <v>37617.974143718733</v>
-      </c>
+      <c r="N25" s="5"/>
       <c r="O25" s="5">
         <v>19166.341385098109</v>
       </c>
@@ -1580,7 +1492,7 @@
         <v>2048</v>
       </c>
       <c r="C26" s="5">
-        <v>1062.282033869428</v>
+        <v>1581.0403219366854</v>
       </c>
       <c r="D26" s="5">
         <v>-36256.629550042744</v>
@@ -1588,16 +1500,14 @@
       <c r="E26" s="5">
         <v>65371.712835673432</v>
       </c>
-      <c r="F26" s="5">
-        <v>8278.9794027489297</v>
-      </c>
+      <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5">
-        <v>-1045.1796218484294</v>
+        <v>-602.83404000731252</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5">
-        <v>790.38698278973141</v>
+        <v>1343.9678760043869</v>
       </c>
       <c r="K26" s="5">
         <f t="shared" si="1"/>
@@ -1611,9 +1521,7 @@
         <f t="shared" si="1"/>
         <v>4183.4156700795629</v>
       </c>
-      <c r="N26" s="5">
-        <v>8315.6439090414751</v>
-      </c>
+      <c r="N26" s="5"/>
       <c r="O26" s="5">
         <v>18421.354309677256</v>
       </c>
@@ -1624,7 +1532,7 @@
         <v>2049</v>
       </c>
       <c r="C27" s="5">
-        <v>1075.2996160344092</v>
+        <v>1594.5810839558285</v>
       </c>
       <c r="D27" s="5">
         <v>58720.223253545359</v>
@@ -1632,16 +1540,14 @@
       <c r="E27" s="5">
         <v>176.52578358770324</v>
       </c>
-      <c r="F27" s="5">
-        <v>8351.1674389202817</v>
-      </c>
+      <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5">
-        <v>-1619.4528413006619</v>
+        <v>-1196.1556337972008</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5">
-        <v>-116.07390559453955</v>
+        <v>484.74765683736626</v>
       </c>
       <c r="K27" s="5">
         <f t="shared" si="1"/>
@@ -1655,9 +1561,7 @@
         <f t="shared" si="1"/>
         <v>4371.669375233143</v>
       </c>
-      <c r="N27" s="5">
-        <v>142.91816402348886</v>
-      </c>
+      <c r="N27" s="5"/>
       <c r="O27" s="5">
         <v>19402.446106210256</v>
       </c>
@@ -1668,7 +1572,7 @@
         <v>2050</v>
       </c>
       <c r="C28" s="5">
-        <v>1037.6105067584497</v>
+        <v>1548.3022299844718</v>
       </c>
       <c r="D28" s="5">
         <v>1953.156109231425</v>
@@ -1676,16 +1580,14 @@
       <c r="E28" s="5">
         <v>163.40515541828785</v>
       </c>
-      <c r="F28" s="5">
-        <v>8321.4072834855524</v>
-      </c>
+      <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5">
-        <v>-1619.5320044668408</v>
+        <v>-1214.4629063774044</v>
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5">
-        <v>-227.95215347026419</v>
+        <v>322.39365103692069</v>
       </c>
       <c r="K28" s="5">
         <f t="shared" si="1"/>
@@ -1699,9 +1601,7 @@
         <f t="shared" si="1"/>
         <v>4568.3944971186338</v>
       </c>
-      <c r="N28" s="5">
-        <v>207.9510466375614</v>
-      </c>
+      <c r="N28" s="5"/>
       <c r="O28" s="5">
         <v>21169.265550508873</v>
       </c>
@@ -1712,7 +1612,7 @@
         <v>2051</v>
       </c>
       <c r="C29" s="5">
-        <v>997.19595060247661</v>
+        <v>1499.0112710310825</v>
       </c>
       <c r="D29" s="5">
         <v>2076.2237893806973</v>
@@ -1720,16 +1620,14 @@
       <c r="E29" s="5">
         <v>115.73315299785321</v>
       </c>
-      <c r="F29" s="5">
-        <v>9144.8197090018821</v>
-      </c>
+      <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5">
-        <v>-1548.3264858205901</v>
+        <v>-1160.7005546345265</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5">
-        <v>-184.46003839554967</v>
+        <v>306.42095629284051</v>
       </c>
       <c r="K29" s="5">
         <f t="shared" si="1"/>
@@ -1743,9 +1641,7 @@
         <f t="shared" si="1"/>
         <v>4773.972249488972</v>
       </c>
-      <c r="N29" s="5">
-        <v>3720.1942824702533</v>
-      </c>
+      <c r="N29" s="5"/>
       <c r="O29" s="5">
         <v>20989.256995824366</v>
       </c>
@@ -1756,7 +1652,7 @@
         <v>2052</v>
       </c>
       <c r="C30" s="5">
-        <v>1275.691675692382</v>
+        <v>1790.0151395634389</v>
       </c>
       <c r="D30" s="5">
         <v>5663.0097529148252</v>
@@ -1764,16 +1660,14 @@
       <c r="E30" s="5">
         <v>91.809703028503719</v>
       </c>
-      <c r="F30" s="5">
-        <v>9162.796070732622</v>
-      </c>
+      <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5">
-        <v>-17113.236494752273</v>
+        <v>-13756.681779200566</v>
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5">
-        <v>-106.31302552011442</v>
+        <v>337.07333368268081</v>
       </c>
       <c r="K30" s="5">
         <f t="shared" ref="K30:M38" si="2">K29*1.045</f>
@@ -1787,9 +1681,7 @@
         <f t="shared" si="2"/>
         <v>4988.8010007159755</v>
       </c>
-      <c r="N30" s="5">
-        <v>-13346.299401545604</v>
-      </c>
+      <c r="N30" s="5"/>
       <c r="O30" s="5">
         <v>21125.568010647345</v>
       </c>
@@ -1800,7 +1692,7 @@
         <v>2053</v>
       </c>
       <c r="C31" s="5">
-        <v>874.40687200636512</v>
+        <v>1235.6059424382429</v>
       </c>
       <c r="D31" s="5">
         <v>2025.9664180611614</v>
@@ -1808,14 +1700,12 @@
       <c r="E31" s="5">
         <v>0</v>
       </c>
-      <c r="F31" s="5">
-        <v>9216.2516001340518</v>
-      </c>
+      <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5">
-        <v>13.935187786349861</v>
+        <v>450.20155415702357</v>
       </c>
       <c r="K31" s="5">
         <f t="shared" si="2"/>
@@ -1829,9 +1719,7 @@
         <f t="shared" si="2"/>
         <v>5213.2970457481943</v>
       </c>
-      <c r="N31" s="5">
-        <v>-302.12659846118009</v>
-      </c>
+      <c r="N31" s="5"/>
       <c r="O31" s="5">
         <v>6548.0965375347387</v>
       </c>
@@ -1842,20 +1730,18 @@
         <v>2054</v>
       </c>
       <c r="C32" s="5">
-        <v>260.03440681628842</v>
+        <v>425.02205054119838</v>
       </c>
       <c r="D32" s="5">
         <v>1919.8539728117053</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="5">
-        <v>9262.1506561333863</v>
-      </c>
+      <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5">
-        <v>81.213714187589304</v>
+        <v>480.25081488405533</v>
       </c>
       <c r="K32" s="5">
         <f t="shared" si="2"/>
@@ -1869,9 +1755,7 @@
         <f t="shared" si="2"/>
         <v>5447.8954128068626</v>
       </c>
-      <c r="N32" s="5">
-        <v>-243.49977630496312</v>
-      </c>
+      <c r="N32" s="5"/>
       <c r="O32" s="5">
         <v>5188.8253978749399</v>
       </c>
@@ -1882,20 +1766,18 @@
         <v>2055</v>
       </c>
       <c r="C33" s="5">
-        <v>-3184.8227946917996</v>
+        <v>-3323.1154015438683</v>
       </c>
       <c r="D33" s="5">
         <v>1809.1392026497824</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="5">
-        <v>9211.7283853004719</v>
-      </c>
+      <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5">
-        <v>-210.5734693421868</v>
+        <v>126.67681954803932</v>
       </c>
       <c r="K33" s="5">
         <f t="shared" si="2"/>
@@ -1909,9 +1791,7 @@
         <f t="shared" si="2"/>
         <v>5693.050706383171</v>
       </c>
-      <c r="N33" s="5">
-        <v>-198.21412230559554</v>
-      </c>
+      <c r="N33" s="5"/>
       <c r="O33" s="5">
         <v>4226.6679307624145</v>
       </c>
@@ -1926,14 +1806,12 @@
         <v>-438.17127495682212</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="5">
-        <v>10226.484665801081</v>
-      </c>
+      <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5">
-        <v>-583.55332889163435</v>
+        <v>-294.27633282098503</v>
       </c>
       <c r="K34" s="5">
         <f t="shared" si="2"/>
@@ -1947,9 +1825,7 @@
         <f t="shared" si="2"/>
         <v>5949.2379881704137</v>
       </c>
-      <c r="N34" s="5">
-        <v>-335.12613459246893</v>
-      </c>
+      <c r="N34" s="5"/>
       <c r="O34" s="5">
         <v>3261.4552517639413</v>
       </c>
@@ -1964,14 +1840,12 @@
         <v>1515.8477492685827</v>
       </c>
       <c r="E35" s="5"/>
-      <c r="F35" s="5">
-        <v>10213.216200994053</v>
-      </c>
+      <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5">
-        <v>-978.1043834942775</v>
+        <v>-912.57279272100948</v>
       </c>
       <c r="K35" s="5">
         <f t="shared" si="2"/>
@@ -1985,9 +1859,7 @@
         <f t="shared" si="2"/>
         <v>6216.9536976380823</v>
       </c>
-      <c r="N35" s="5">
-        <v>-770.54571906388662</v>
-      </c>
+      <c r="N35" s="5"/>
       <c r="O35" s="5">
         <v>1144.9852322624533</v>
       </c>
@@ -2002,14 +1874,12 @@
         <v>1521.1057646670865</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="5">
-        <v>10248.472431009239</v>
-      </c>
+      <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5">
-        <v>-931.82308742781004</v>
+        <v>-879.9105266654185</v>
       </c>
       <c r="K36" s="5">
         <f t="shared" si="2"/>
@@ -2023,9 +1893,7 @@
         <f t="shared" si="2"/>
         <v>6496.7166140317959</v>
       </c>
-      <c r="N36" s="5">
-        <v>-9868.2151940255881</v>
-      </c>
+      <c r="N36" s="5"/>
       <c r="O36" s="5"/>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.25">
@@ -2038,14 +1906,12 @@
         <v>1525.4028087225845</v>
       </c>
       <c r="E37" s="5"/>
-      <c r="F37" s="5">
-        <v>10277.342439080616</v>
-      </c>
+      <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5">
-        <v>-896.1880222748066</v>
+        <v>-841.27466267220996</v>
       </c>
       <c r="K37" s="5">
         <f t="shared" si="2"/>
@@ -2071,14 +1937,12 @@
         <v>17770.841584153739</v>
       </c>
       <c r="E38" s="5"/>
-      <c r="F38" s="5">
-        <v>126239.11166860364</v>
-      </c>
+      <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5">
-        <v>-248.57038566350593</v>
+        <v>-190.4831126001113</v>
       </c>
       <c r="K38" s="5">
         <f t="shared" si="2"/>
@@ -2116,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="10">
-        <v>9.2337396205789979</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
@@ -2124,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="12">
-        <v>12.522138549936855</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
@@ -2132,7 +1996,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="12">
-        <v>14.433849503735471</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
@@ -2140,28 +2004,26 @@
         <v>3</v>
       </c>
       <c r="D6" s="12">
-        <v>12.162680142300024</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="12">
-        <v>12.529197741721557</v>
-      </c>
+      <c r="D7" s="12"/>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="12">
-        <v>6.1975707644774349</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" s="12">
         <v>8.190683748997424</v>
@@ -2172,7 +2034,7 @@
         <v>7</v>
       </c>
       <c r="D10" s="12">
-        <v>6.6642665374344405</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
@@ -2213,26 +2075,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020E4BAF79DB213408BB296F3F8F32329" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9679123e7a51fb6c2fee49c985862cfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457" xmlns:ns3="f0bab05a-e9c1-4e32-93e9-8363aec9c620" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ddaff962f7439efafa6fc254a8996caa" ns2:_="" ns3:_="">
     <xsd:import namespace="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
@@ -2467,10 +2309,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
+    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2487,20 +2360,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
-    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/irrdash3.xlsx
+++ b/irrdash3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.russo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED15E5E3-5573-4AB7-B34C-EB2BE8E437F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA07E12A-2E00-4873-A319-850763EF1862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
-  <si>
-    <t>CPLE6</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>EQTL3</t>
   </si>
@@ -87,7 +84,7 @@
     <t>CPLE3</t>
   </si>
   <si>
-    <t>AXIA6</t>
+    <t>AXIA3</t>
   </si>
 </sst>
 </file>
@@ -574,51 +571,51 @@
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -647,7 +644,9 @@
       <c r="E4" s="5">
         <v>1423.5911688211188</v>
       </c>
-      <c r="F4" s="5"/>
+      <c r="F4" s="5">
+        <v>-3213.7582022461929</v>
+      </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5">
         <v>-8.7620158507064616</v>
@@ -667,7 +666,7 @@
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5">
-        <v>18511.406301685623</v>
+        <v>18979.748191630773</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
@@ -684,7 +683,9 @@
       <c r="E5" s="5">
         <v>836.48604610360985</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="5">
+        <v>2153.7683972047375</v>
+      </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
         <v>952.98742767157978</v>
@@ -704,7 +705,7 @@
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5">
-        <v>22879.286074147032</v>
+        <v>18413.86475407553</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
@@ -721,7 +722,9 @@
       <c r="E6" s="5">
         <v>1886.5332002018404</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="F6" s="5">
+        <v>7430.7261851717485</v>
+      </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
         <v>6589.9422482750315</v>
@@ -741,7 +744,7 @@
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5">
-        <v>21037.072244304934</v>
+        <v>15989.244257070595</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
@@ -758,7 +761,9 @@
       <c r="E7" s="5">
         <v>2728.8526153584262</v>
       </c>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5">
+        <v>5868.3860394759795</v>
+      </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
         <v>5536.1237456745603</v>
@@ -778,7 +783,7 @@
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5">
-        <v>14257.130957783082</v>
+        <v>14727.36986785778</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
@@ -795,7 +800,9 @@
       <c r="E8" s="5">
         <v>1996.046006674206</v>
       </c>
-      <c r="F8" s="5"/>
+      <c r="F8" s="5">
+        <v>10459.523070276808</v>
+      </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
         <v>12017.286584211188</v>
@@ -815,7 +822,7 @@
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5">
-        <v>14572.640722376331</v>
+        <v>8099.5534825768154</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
@@ -832,7 +839,9 @@
       <c r="E9" s="5">
         <v>3040.4333366384258</v>
       </c>
-      <c r="F9" s="5"/>
+      <c r="F9" s="5">
+        <v>12726.938192010584</v>
+      </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
         <v>8473.7455168781198</v>
@@ -852,7 +861,7 @@
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5">
-        <v>14256.83359063529</v>
+        <v>16443.830669127274</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
@@ -869,7 +878,9 @@
       <c r="E10" s="5">
         <v>3079.6282281473705</v>
       </c>
-      <c r="F10" s="5"/>
+      <c r="F10" s="5">
+        <v>14657.057428864216</v>
+      </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
         <v>11404.257473885451</v>
@@ -889,7 +900,7 @@
       </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5">
-        <v>14916.449828221348</v>
+        <v>16459.568026111487</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
@@ -906,7 +917,9 @@
       <c r="E11" s="5">
         <v>3365.750967532942</v>
       </c>
-      <c r="F11" s="5"/>
+      <c r="F11" s="5">
+        <v>14337.616475338573</v>
+      </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
         <v>9338.3280772234048</v>
@@ -926,7 +939,7 @@
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5">
-        <v>14802.022900230375</v>
+        <v>16914.43077495979</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
@@ -943,7 +956,9 @@
       <c r="E12" s="5">
         <v>3998.2297037974399</v>
       </c>
-      <c r="F12" s="5"/>
+      <c r="F12" s="5">
+        <v>14365.203232180073</v>
+      </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
         <v>9426.7694638763442</v>
@@ -963,7 +978,7 @@
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5">
-        <v>14927.501604703333</v>
+        <v>20543.191589300575</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
@@ -980,7 +995,9 @@
       <c r="E13" s="5">
         <v>3357.9892161586899</v>
       </c>
-      <c r="F13" s="5"/>
+      <c r="F13" s="5">
+        <v>11225.287435689021</v>
+      </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5">
         <v>9290.320997467421</v>
@@ -1003,7 +1020,7 @@
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5">
-        <v>8966.776435412432</v>
+        <v>17790.242781651366</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
@@ -1020,7 +1037,9 @@
       <c r="E14" s="5">
         <v>3890.7284841014853</v>
       </c>
-      <c r="F14" s="5"/>
+      <c r="F14" s="5">
+        <v>12526.473467906662</v>
+      </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
         <v>8673.6495661046774</v>
@@ -1043,7 +1062,7 @@
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5">
-        <v>9170.2795180922367</v>
+        <v>20822.020304664984</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
@@ -1060,7 +1079,9 @@
       <c r="E15" s="5">
         <v>3795.421343208634</v>
       </c>
-      <c r="F15" s="5"/>
+      <c r="F15" s="5">
+        <v>12098.001078854475</v>
+      </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
         <v>8188.6870790363791</v>
@@ -1083,7 +1104,7 @@
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5">
-        <v>9901.0095168224398</v>
+        <v>17212.445226073032</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
@@ -1100,7 +1121,9 @@
       <c r="E16" s="5">
         <v>4241.1276645324469</v>
       </c>
-      <c r="F16" s="5"/>
+      <c r="F16" s="5">
+        <v>11794.707213518148</v>
+      </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
         <v>8004.3987166707338</v>
@@ -1123,7 +1146,7 @@
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5">
-        <v>16924.708304675674</v>
+        <v>17320.053746271926</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
@@ -1140,7 +1163,9 @@
       <c r="E17" s="5">
         <v>4700.1076438236432</v>
       </c>
-      <c r="F17" s="5"/>
+      <c r="F17" s="5">
+        <v>10033.941187796812</v>
+      </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
         <v>7114.7800115611963</v>
@@ -1163,7 +1188,7 @@
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5">
-        <v>18304.907510996669</v>
+        <v>17837.796468745979</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
@@ -1180,7 +1205,9 @@
       <c r="E18" s="5">
         <v>4448.8476307615656</v>
       </c>
-      <c r="F18" s="5"/>
+      <c r="F18" s="5">
+        <v>12885.809456803918</v>
+      </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
         <v>8959.0426799030829</v>
@@ -1203,7 +1230,7 @@
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5">
-        <v>19338.066657106887</v>
+        <v>11975.156503692111</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
@@ -1220,7 +1247,9 @@
       <c r="E19" s="5">
         <v>4404.6638333651717</v>
       </c>
-      <c r="F19" s="5"/>
+      <c r="F19" s="5">
+        <v>11906.949719039918</v>
+      </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
         <v>5706.5892170742209</v>
@@ -1243,7 +1272,7 @@
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5">
-        <v>20929.557974011255</v>
+        <v>17751.944353503422</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
@@ -1260,7 +1289,9 @@
       <c r="E20" s="5">
         <v>4322.8251616964926</v>
       </c>
-      <c r="F20" s="5"/>
+      <c r="F20" s="5">
+        <v>6998.5676824367993</v>
+      </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5">
         <v>5791.5387040282367</v>
@@ -1283,7 +1314,7 @@
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5">
-        <v>28513.605545167349</v>
+        <v>38535.962917223864</v>
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
@@ -1300,7 +1331,9 @@
       <c r="E21" s="5">
         <v>4704.9869228474563</v>
       </c>
-      <c r="F21" s="5"/>
+      <c r="F21" s="5">
+        <v>6268.3530826487331</v>
+      </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
         <v>3723.3268802003786</v>
@@ -1323,7 +1356,7 @@
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5">
-        <v>19008.491823315748</v>
+        <v>28948.361031309589</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
@@ -1340,7 +1373,9 @@
       <c r="E22" s="5">
         <v>5466.3907696940523</v>
       </c>
-      <c r="F22" s="5"/>
+      <c r="F22" s="5">
+        <v>7082.4336494526806</v>
+      </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5">
         <v>2227.0346985504361</v>
@@ -1363,7 +1398,7 @@
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5">
-        <v>19847.81212405007</v>
+        <v>8308.653322847611</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
@@ -1380,7 +1415,9 @@
       <c r="E23" s="5">
         <v>6800.1708681005994</v>
       </c>
-      <c r="F23" s="5"/>
+      <c r="F23" s="5">
+        <v>8080.1271188766168</v>
+      </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
         <v>661.03155598403737</v>
@@ -1403,7 +1440,7 @@
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5">
-        <v>20539.534716877293</v>
+        <v>10974.815190337027</v>
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
@@ -1420,7 +1457,9 @@
       <c r="E24" s="5">
         <v>4836.6248297612428</v>
       </c>
-      <c r="F24" s="5"/>
+      <c r="F24" s="5">
+        <v>9986.8391260733788</v>
+      </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
         <v>-649.48826947455473</v>
@@ -1443,7 +1482,7 @@
       </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5">
-        <v>20702.885848859736</v>
+        <v>12390.409145349473</v>
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
@@ -1460,7 +1499,9 @@
       <c r="E25" s="5">
         <v>4570.7074782877553</v>
       </c>
-      <c r="F25" s="5"/>
+      <c r="F25" s="5">
+        <v>9929.3387717870937</v>
+      </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5">
         <v>-758.26620108825864</v>
@@ -1483,7 +1524,7 @@
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5">
-        <v>19166.341385098109</v>
+        <v>42832.694420480984</v>
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
@@ -1500,7 +1541,9 @@
       <c r="E26" s="5">
         <v>65371.712835673432</v>
       </c>
-      <c r="F26" s="5"/>
+      <c r="F26" s="5">
+        <v>9929.1475016048498</v>
+      </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5">
         <v>-602.83404000731252</v>
@@ -1523,7 +1566,7 @@
       </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5">
-        <v>18421.354309677256</v>
+        <v>14187.758292172577</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.25">
@@ -1540,7 +1583,9 @@
       <c r="E27" s="5">
         <v>176.52578358770324</v>
       </c>
-      <c r="F27" s="5"/>
+      <c r="F27" s="5">
+        <v>9910.7944726613368</v>
+      </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5">
         <v>-1196.1556337972008</v>
@@ -1563,7 +1608,7 @@
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5">
-        <v>19402.446106210256</v>
+        <v>7000.1831282626235</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
@@ -1580,7 +1625,9 @@
       <c r="E28" s="5">
         <v>163.40515541828785</v>
       </c>
-      <c r="F28" s="5"/>
+      <c r="F28" s="5">
+        <v>10680.813756512784</v>
+      </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5">
         <v>-1214.4629063774044</v>
@@ -1603,7 +1650,7 @@
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5">
-        <v>21169.265550508873</v>
+        <v>6676.8255862494798</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
@@ -1620,7 +1667,9 @@
       <c r="E29" s="5">
         <v>115.73315299785321</v>
       </c>
-      <c r="F29" s="5"/>
+      <c r="F29" s="5">
+        <v>12525.515837754807</v>
+      </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5">
         <v>-1160.7005546345265</v>
@@ -1643,7 +1692,7 @@
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5">
-        <v>20989.256995824366</v>
+        <v>9971.7076869591474</v>
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
@@ -1660,7 +1709,9 @@
       <c r="E30" s="5">
         <v>91.809703028503719</v>
       </c>
-      <c r="F30" s="5"/>
+      <c r="F30" s="5">
+        <v>12438.87888455006</v>
+      </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5">
         <v>-13756.681779200566</v>
@@ -1683,7 +1734,7 @@
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5">
-        <v>21125.568010647345</v>
+        <v>7192.4997346401542</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
@@ -1700,7 +1751,9 @@
       <c r="E31" s="5">
         <v>0</v>
       </c>
-      <c r="F31" s="5"/>
+      <c r="F31" s="5">
+        <v>12410.807562833361</v>
+      </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -1720,9 +1773,7 @@
         <v>5213.2970457481943</v>
       </c>
       <c r="N31" s="5"/>
-      <c r="O31" s="5">
-        <v>6548.0965375347387</v>
-      </c>
+      <c r="O31" s="5"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
@@ -1736,7 +1787,9 @@
         <v>1919.8539728117053</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="F32" s="5">
+        <v>12365.687941287604</v>
+      </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -1756,9 +1809,7 @@
         <v>5447.8954128068626</v>
       </c>
       <c r="N32" s="5"/>
-      <c r="O32" s="5">
-        <v>5188.8253978749399</v>
-      </c>
+      <c r="O32" s="5"/>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
@@ -1772,7 +1823,9 @@
         <v>1809.1392026497824</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
+      <c r="F33" s="5">
+        <v>13093.481402437206</v>
+      </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -1792,9 +1845,7 @@
         <v>5693.050706383171</v>
       </c>
       <c r="N33" s="5"/>
-      <c r="O33" s="5">
-        <v>4226.6679307624145</v>
-      </c>
+      <c r="O33" s="5"/>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
@@ -1806,7 +1857,9 @@
         <v>-438.17127495682212</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="F34" s="5">
+        <v>15495.394835911449</v>
+      </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
@@ -1826,9 +1879,7 @@
         <v>5949.2379881704137</v>
       </c>
       <c r="N34" s="5"/>
-      <c r="O34" s="5">
-        <v>3261.4552517639413</v>
-      </c>
+      <c r="O34" s="5"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
@@ -1840,7 +1891,9 @@
         <v>1515.8477492685827</v>
       </c>
       <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="F35" s="5">
+        <v>15043.078037869464</v>
+      </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
@@ -1860,9 +1913,7 @@
         <v>6216.9536976380823</v>
       </c>
       <c r="N35" s="5"/>
-      <c r="O35" s="5">
-        <v>1144.9852322624533</v>
-      </c>
+      <c r="O35" s="5"/>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
@@ -1874,7 +1925,9 @@
         <v>1521.1057646670865</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="F36" s="5">
+        <v>14732.658259766657</v>
+      </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
@@ -1906,7 +1959,9 @@
         <v>1525.4028087225845</v>
       </c>
       <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="F37" s="5">
+        <v>15031.126614377423</v>
+      </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
@@ -1937,7 +1992,9 @@
         <v>17770.841584153739</v>
       </c>
       <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="F38" s="5">
+        <v>239244.34860275887</v>
+      </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
@@ -1972,12 +2029,12 @@
     <row r="2" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="7"/>
       <c r="D2" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C3" s="9" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D3" s="10">
         <v>7</v>
@@ -1985,7 +2042,7 @@
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" s="11" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="12">
         <v>10.5</v>
@@ -1993,7 +2050,7 @@
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" s="11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="12">
         <v>10</v>
@@ -2001,21 +2058,19 @@
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="12">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="11" t="s">
-        <v>4</v>
-      </c>
+      <c r="C7" s="11"/>
       <c r="D7" s="12"/>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="12">
         <v>6</v>
@@ -2023,23 +2078,23 @@
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C9" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="12">
-        <v>8.190683748997424</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C10" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="12">
-        <v>6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C11" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" s="12">
         <v>11.006125118224018</v>
@@ -2047,7 +2102,7 @@
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="12">
         <v>11.671918388589615</v>
@@ -2055,19 +2110,15 @@
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" s="12">
         <v>11.199476972806313</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="12">
-        <v>8.1906837489974222</v>
-      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2075,6 +2126,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020E4BAF79DB213408BB296F3F8F32329" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9679123e7a51fb6c2fee49c985862cfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457" xmlns:ns3="f0bab05a-e9c1-4e32-93e9-8363aec9c620" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ddaff962f7439efafa6fc254a8996caa" ns2:_="" ns3:_="">
     <xsd:import namespace="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
@@ -2309,27 +2380,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47140DD7-5C12-4BA5-9C24-A1CF0564C7A2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
+    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2346,23 +2416,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47140DD7-5C12-4BA5-9C24-A1CF0564C7A2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
-    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/irrdash3.xlsx
+++ b/irrdash3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.russo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA07E12A-2E00-4873-A319-850763EF1862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD4D86F-94CE-45FD-8C9F-CD35D62D1ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2073,7 +2073,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="12">
-        <v>6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
@@ -2081,7 +2081,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="12">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
@@ -2126,26 +2126,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020E4BAF79DB213408BB296F3F8F32329" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9679123e7a51fb6c2fee49c985862cfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457" xmlns:ns3="f0bab05a-e9c1-4e32-93e9-8363aec9c620" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ddaff962f7439efafa6fc254a8996caa" ns2:_="" ns3:_="">
     <xsd:import namespace="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
@@ -2380,10 +2360,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
+    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2400,20 +2411,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
-    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/irrdash3.xlsx
+++ b/irrdash3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.russo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD4D86F-94CE-45FD-8C9F-CD35D62D1ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{967E21A2-DC17-41B5-9541-52DB362B214A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -684,7 +684,7 @@
         <v>836.48604610360985</v>
       </c>
       <c r="F5" s="5">
-        <v>2153.7683972047375</v>
+        <v>1992.5790328815574</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
@@ -723,7 +723,7 @@
         <v>1886.5332002018404</v>
       </c>
       <c r="F6" s="5">
-        <v>7430.7261851717485</v>
+        <v>7329.4140739717586</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
@@ -762,7 +762,7 @@
         <v>2728.8526153584262</v>
       </c>
       <c r="F7" s="5">
-        <v>5868.3860394759795</v>
+        <v>5033.6896474707046</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
@@ -801,7 +801,7 @@
         <v>1996.046006674206</v>
       </c>
       <c r="F8" s="5">
-        <v>10459.523070276808</v>
+        <v>10151.841225696608</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
@@ -840,7 +840,7 @@
         <v>3040.4333366384258</v>
       </c>
       <c r="F9" s="5">
-        <v>12726.938192010584</v>
+        <v>13047.902210151391</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
@@ -879,7 +879,7 @@
         <v>3079.6282281473705</v>
       </c>
       <c r="F10" s="5">
-        <v>14657.057428864216</v>
+        <v>16201.423462993538</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
@@ -918,7 +918,7 @@
         <v>3365.750967532942</v>
       </c>
       <c r="F11" s="5">
-        <v>14337.616475338573</v>
+        <v>15709.19927115742</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
@@ -957,7 +957,7 @@
         <v>3998.2297037974399</v>
       </c>
       <c r="F12" s="5">
-        <v>14365.203232180073</v>
+        <v>15868.98572730064</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
@@ -996,7 +996,7 @@
         <v>3357.9892161586899</v>
       </c>
       <c r="F13" s="5">
-        <v>11225.287435689021</v>
+        <v>12859.447589777848</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5">
@@ -1038,7 +1038,7 @@
         <v>3890.7284841014853</v>
       </c>
       <c r="F14" s="5">
-        <v>12526.473467906662</v>
+        <v>14281.254281581185</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
@@ -1080,7 +1080,7 @@
         <v>3795.421343208634</v>
       </c>
       <c r="F15" s="5">
-        <v>12098.001078854475</v>
+        <v>13964.375731795819</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
@@ -1122,7 +1122,7 @@
         <v>4241.1276645324469</v>
       </c>
       <c r="F16" s="5">
-        <v>11794.707213518148</v>
+        <v>13764.32442047207</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
@@ -1164,7 +1164,7 @@
         <v>4700.1076438236432</v>
       </c>
       <c r="F17" s="5">
-        <v>10033.941187796812</v>
+        <v>9552.9699081411782</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
@@ -1206,7 +1206,7 @@
         <v>4448.8476307615656</v>
       </c>
       <c r="F18" s="5">
-        <v>12885.809456803918</v>
+        <v>13851.400921987946</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
@@ -1248,7 +1248,7 @@
         <v>4404.6638333651717</v>
       </c>
       <c r="F19" s="5">
-        <v>11906.949719039918</v>
+        <v>14029.085554077283</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
@@ -1290,7 +1290,7 @@
         <v>4322.8251616964926</v>
       </c>
       <c r="F20" s="5">
-        <v>6998.5676824367993</v>
+        <v>9217.1673925462674</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5">
@@ -1332,7 +1332,7 @@
         <v>4704.9869228474563</v>
       </c>
       <c r="F21" s="5">
-        <v>6268.3530826487331</v>
+        <v>8554.1344001208017</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
@@ -1374,7 +1374,7 @@
         <v>5466.3907696940523</v>
       </c>
       <c r="F22" s="5">
-        <v>7082.4336494526806</v>
+        <v>9430.3689422011157</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5">
@@ -1416,7 +1416,7 @@
         <v>6800.1708681005994</v>
       </c>
       <c r="F23" s="5">
-        <v>8080.1271188766168</v>
+        <v>10485.565004884022</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
@@ -1458,7 +1458,7 @@
         <v>4836.6248297612428</v>
       </c>
       <c r="F24" s="5">
-        <v>9986.8391260733788</v>
+        <v>12445.476316176846</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
@@ -1500,7 +1500,7 @@
         <v>4570.7074782877553</v>
       </c>
       <c r="F25" s="5">
-        <v>9929.3387717870937</v>
+        <v>12437.194019649436</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5">
@@ -1542,7 +1542,7 @@
         <v>65371.712835673432</v>
       </c>
       <c r="F26" s="5">
-        <v>9929.1475016048498</v>
+        <v>12482.537503177165</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5">
@@ -1584,7 +1584,7 @@
         <v>176.52578358770324</v>
       </c>
       <c r="F27" s="5">
-        <v>9910.7944726613368</v>
+        <v>12506.311569243899</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5">
@@ -1626,7 +1626,7 @@
         <v>163.40515541828785</v>
       </c>
       <c r="F28" s="5">
-        <v>10680.813756512784</v>
+        <v>13315.305306439397</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5">
@@ -1668,7 +1668,7 @@
         <v>115.73315299785321</v>
       </c>
       <c r="F29" s="5">
-        <v>12525.515837754807</v>
+        <v>15196.065131826799</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5">
@@ -1710,7 +1710,7 @@
         <v>91.809703028503719</v>
       </c>
       <c r="F30" s="5">
-        <v>12438.87888455006</v>
+        <v>15142.787489691193</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5">
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="5">
-        <v>12410.807562833361</v>
+        <v>15145.578987082663</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5">
-        <v>12365.687941287604</v>
+        <v>15129.01252124595</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5">
-        <v>13093.481402437206</v>
+        <v>15883.22232168353</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5">
-        <v>15495.394835911449</v>
+        <v>18309.575189750867</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5">
-        <v>15043.078037869464</v>
+        <v>14509.833795732029</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5">
-        <v>14732.658259766657</v>
+        <v>10879.018171786525</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5">
-        <v>15031.126614377423</v>
+        <v>14806.124169231436</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5">
-        <v>239244.34860275887</v>
+        <v>286027.70157690934</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -2126,6 +2126,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020E4BAF79DB213408BB296F3F8F32329" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9679123e7a51fb6c2fee49c985862cfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457" xmlns:ns3="f0bab05a-e9c1-4e32-93e9-8363aec9c620" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ddaff962f7439efafa6fc254a8996caa" ns2:_="" ns3:_="">
     <xsd:import namespace="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
@@ -2360,27 +2380,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47140DD7-5C12-4BA5-9C24-A1CF0564C7A2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
+    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2397,23 +2416,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47140DD7-5C12-4BA5-9C24-A1CF0564C7A2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
-    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/irrdash3.xlsx
+++ b/irrdash3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.russo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{967E21A2-DC17-41B5-9541-52DB362B214A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF6B61E1-AFA8-42D3-AF41-589DF6ED63AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -639,7 +639,7 @@
         <v>2745.4364798654174</v>
       </c>
       <c r="D4" s="5">
-        <v>2346.2961342640269</v>
+        <v>906.20902652957579</v>
       </c>
       <c r="E4" s="5">
         <v>1423.5911688211188</v>
@@ -678,7 +678,7 @@
         <v>5030.9414324565514</v>
       </c>
       <c r="D5" s="5">
-        <v>1008.0047307031887</v>
+        <v>213.72116190750472</v>
       </c>
       <c r="E5" s="5">
         <v>836.48604610360985</v>
@@ -717,7 +717,7 @@
         <v>4878.854572172454</v>
       </c>
       <c r="D6" s="5">
-        <v>-383.33124786745475</v>
+        <v>-537.15129089311472</v>
       </c>
       <c r="E6" s="5">
         <v>1886.5332002018404</v>
@@ -756,7 +756,7 @@
         <v>4847.5209112119855</v>
       </c>
       <c r="D7" s="5">
-        <v>2230.8222624931559</v>
+        <v>1682.9507788822602</v>
       </c>
       <c r="E7" s="5">
         <v>2728.8526153584262</v>
@@ -795,7 +795,7 @@
         <v>5160.437064035852</v>
       </c>
       <c r="D8" s="5">
-        <v>5320.9952403656134</v>
+        <v>5255.4599833798002</v>
       </c>
       <c r="E8" s="5">
         <v>1996.046006674206</v>
@@ -834,7 +834,7 @@
         <v>6196.4049493969596</v>
       </c>
       <c r="D9" s="5">
-        <v>5838.2169035851375</v>
+        <v>6296.2382546290301</v>
       </c>
       <c r="E9" s="5">
         <v>3040.4333366384258</v>
@@ -873,7 +873,7 @@
         <v>6699.1790561707985</v>
       </c>
       <c r="D10" s="5">
-        <v>7470.658368937854</v>
+        <v>8436.3555138061729</v>
       </c>
       <c r="E10" s="5">
         <v>3079.6282281473705</v>
@@ -912,7 +912,7 @@
         <v>6773.3605098858025</v>
       </c>
       <c r="D11" s="5">
-        <v>5493.0997048113531</v>
+        <v>6426.1269359699909</v>
       </c>
       <c r="E11" s="5">
         <v>3365.750967532942</v>
@@ -951,7 +951,7 @@
         <v>6876.5340588649724</v>
       </c>
       <c r="D12" s="5">
-        <v>11308.504943659194</v>
+        <v>12233.660674885701</v>
       </c>
       <c r="E12" s="5">
         <v>3998.2297037974399</v>
@@ -990,7 +990,7 @@
         <v>7138.8046805764006</v>
       </c>
       <c r="D13" s="5">
-        <v>11680.517848620657</v>
+        <v>12659.045350191773</v>
       </c>
       <c r="E13" s="5">
         <v>3357.9892161586899</v>
@@ -1032,7 +1032,7 @@
         <v>7109.0430282295492</v>
       </c>
       <c r="D14" s="5">
-        <v>11587.516251420138</v>
+        <v>12306.414228418334</v>
       </c>
       <c r="E14" s="5">
         <v>3890.7284841014853</v>
@@ -1074,7 +1074,7 @@
         <v>7185.1894287338318</v>
       </c>
       <c r="D15" s="5">
-        <v>10348.675117827352</v>
+        <v>11046.719287529615</v>
       </c>
       <c r="E15" s="5">
         <v>3795.421343208634</v>
@@ -1116,7 +1116,7 @@
         <v>7365.6208094844114</v>
       </c>
       <c r="D16" s="5">
-        <v>9768.6833032279974</v>
+        <v>10440.923640693254</v>
       </c>
       <c r="E16" s="5">
         <v>4241.1276645324469</v>
@@ -1158,7 +1158,7 @@
         <v>7508.1630455113282</v>
       </c>
       <c r="D17" s="5">
-        <v>10155.942786401696</v>
+        <v>10200.965639970937</v>
       </c>
       <c r="E17" s="5">
         <v>4700.1076438236432</v>
@@ -1200,7 +1200,7 @@
         <v>7491.1459400575186</v>
       </c>
       <c r="D18" s="5">
-        <v>10330.306705276818</v>
+        <v>10955.139314314256</v>
       </c>
       <c r="E18" s="5">
         <v>4448.8476307615656</v>
@@ -1242,7 +1242,7 @@
         <v>6692.2296027473712</v>
       </c>
       <c r="D19" s="5">
-        <v>9547.3412998822914</v>
+        <v>10440.615645595444</v>
       </c>
       <c r="E19" s="5">
         <v>4404.6638333651717</v>
@@ -1284,7 +1284,7 @@
         <v>10022.354780335389</v>
       </c>
       <c r="D20" s="5">
-        <v>5116.222974985365</v>
+        <v>5481.5721552845898</v>
       </c>
       <c r="E20" s="5">
         <v>4322.8251616964926</v>
@@ -1326,7 +1326,7 @@
         <v>5630.0233805802036</v>
       </c>
       <c r="D21" s="5">
-        <v>5225.6606237213318</v>
+        <v>5587.5251678781215</v>
       </c>
       <c r="E21" s="5">
         <v>4704.9869228474563</v>
@@ -1368,7 +1368,7 @@
         <v>5640.800647683538</v>
       </c>
       <c r="D22" s="5">
-        <v>7421.6683063923683</v>
+        <v>7773.5078665300134</v>
       </c>
       <c r="E22" s="5">
         <v>5466.3907696940523</v>
@@ -1410,7 +1410,7 @@
         <v>-4470.0060412833718</v>
       </c>
       <c r="D23" s="5">
-        <v>8047.2674890790931</v>
+        <v>8550.1529304554442</v>
       </c>
       <c r="E23" s="5">
         <v>6800.1708681005994</v>
@@ -1452,7 +1452,7 @@
         <v>22223.170163740746</v>
       </c>
       <c r="D24" s="5">
-        <v>17133.14369506764</v>
+        <v>17793.833416400517</v>
       </c>
       <c r="E24" s="5">
         <v>4836.6248297612428</v>
@@ -1494,7 +1494,7 @@
         <v>1761.6618872329177</v>
       </c>
       <c r="D25" s="5">
-        <v>6640.3369228731744</v>
+        <v>7293.252979701183</v>
       </c>
       <c r="E25" s="5">
         <v>4570.7074782877553</v>
@@ -1536,7 +1536,7 @@
         <v>1581.0403219366854</v>
       </c>
       <c r="D26" s="5">
-        <v>-36256.629550042744</v>
+        <v>-35609.031760813356</v>
       </c>
       <c r="E26" s="5">
         <v>65371.712835673432</v>
@@ -1578,7 +1578,7 @@
         <v>1594.5810839558285</v>
       </c>
       <c r="D27" s="5">
-        <v>58720.223253545359</v>
+        <v>59360.575510655093</v>
       </c>
       <c r="E27" s="5">
         <v>176.52578358770324</v>
@@ -1620,7 +1620,7 @@
         <v>1548.3022299844718</v>
       </c>
       <c r="D28" s="5">
-        <v>1953.156109231425</v>
+        <v>2719.3363901280768</v>
       </c>
       <c r="E28" s="5">
         <v>163.40515541828785</v>
@@ -1662,7 +1662,7 @@
         <v>1499.0112710310825</v>
       </c>
       <c r="D29" s="5">
-        <v>2076.2237893806973</v>
+        <v>3000.4974286813199</v>
       </c>
       <c r="E29" s="5">
         <v>115.73315299785321</v>
@@ -1704,7 +1704,7 @@
         <v>1790.0151395634389</v>
       </c>
       <c r="D30" s="5">
-        <v>5663.0097529148252</v>
+        <v>6576.6452042020592</v>
       </c>
       <c r="E30" s="5">
         <v>91.809703028503719</v>
@@ -1746,7 +1746,7 @@
         <v>1235.6059424382429</v>
       </c>
       <c r="D31" s="5">
-        <v>2025.9664180611614</v>
+        <v>2932.0266169418528</v>
       </c>
       <c r="E31" s="5">
         <v>0</v>
@@ -1784,7 +1784,7 @@
         <v>425.02205054119838</v>
       </c>
       <c r="D32" s="5">
-        <v>1919.8539728117053</v>
+        <v>2816.5724967717488</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5">
@@ -1820,7 +1820,7 @@
         <v>-3323.1154015438683</v>
       </c>
       <c r="D33" s="5">
-        <v>1809.1392026497824</v>
+        <v>2826.5787744966747</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>-438.17127495682212</v>
+        <v>790.36209178577474</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="5">
-        <v>1515.8477492685827</v>
+        <v>2176.4750693598044</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>1521.1057646670865</v>
+        <v>1631.8527257679787</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="5">
-        <v>1525.4028087225845</v>
+        <v>2220.9186253847151</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>17770.841584153739</v>
+        <v>42904.155236536397</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5">
@@ -2126,26 +2126,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020E4BAF79DB213408BB296F3F8F32329" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9679123e7a51fb6c2fee49c985862cfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457" xmlns:ns3="f0bab05a-e9c1-4e32-93e9-8363aec9c620" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ddaff962f7439efafa6fc254a8996caa" ns2:_="" ns3:_="">
     <xsd:import namespace="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
@@ -2380,10 +2360,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
+    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2400,20 +2411,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
-    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/irrdash3.xlsx
+++ b/irrdash3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.russo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF6B61E1-AFA8-42D3-AF41-589DF6ED63AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A117E90-2A1A-49EA-81DD-B89ADA894169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>EQTL3</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>AXIA3</t>
+  </si>
+  <si>
+    <t>CSMG3</t>
   </si>
 </sst>
 </file>
@@ -557,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:P38"/>
+  <dimension ref="B1:P51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
@@ -611,6 +614,9 @@
       </c>
       <c r="O2" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
@@ -668,10 +674,13 @@
       <c r="O4" s="5">
         <v>18979.748191630773</v>
       </c>
+      <c r="P4" s="5">
+        <v>782.53782767150824</v>
+      </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
-        <f t="shared" ref="B5:B38" si="0">B4+1</f>
+        <f t="shared" ref="B5:B51" si="0">B4+1</f>
         <v>2027</v>
       </c>
       <c r="C5" s="5">
@@ -707,6 +716,9 @@
       <c r="O5" s="5">
         <v>18413.86475407553</v>
       </c>
+      <c r="P5" s="5">
+        <v>-388.56802401671359</v>
+      </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
@@ -746,6 +758,9 @@
       <c r="O6" s="5">
         <v>15989.244257070595</v>
       </c>
+      <c r="P6" s="5">
+        <v>749.7765817929162</v>
+      </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
@@ -785,6 +800,9 @@
       <c r="O7" s="5">
         <v>14727.36986785778</v>
       </c>
+      <c r="P7" s="5">
+        <v>1128.9045609814541</v>
+      </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
@@ -824,6 +842,9 @@
       <c r="O8" s="5">
         <v>8099.5534825768154</v>
       </c>
+      <c r="P8" s="5">
+        <v>1097.1357449407799</v>
+      </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
@@ -863,6 +884,9 @@
       <c r="O9" s="5">
         <v>16443.830669127274</v>
       </c>
+      <c r="P9" s="5">
+        <v>-1187.7051190379329</v>
+      </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
@@ -902,6 +926,9 @@
       <c r="O10" s="5">
         <v>16459.568026111487</v>
       </c>
+      <c r="P10" s="5">
+        <v>3053.4660067585714</v>
+      </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
@@ -941,6 +968,9 @@
       <c r="O11" s="5">
         <v>16914.43077495979</v>
       </c>
+      <c r="P11" s="5">
+        <v>4211.1594704752606</v>
+      </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
@@ -980,6 +1010,9 @@
       <c r="O12" s="5">
         <v>20543.191589300575</v>
       </c>
+      <c r="P12" s="5">
+        <v>4624.3053049833024</v>
+      </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
@@ -1022,6 +1055,9 @@
       <c r="O13" s="5">
         <v>17790.242781651366</v>
       </c>
+      <c r="P13" s="5">
+        <v>503.05313709281</v>
+      </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
@@ -1064,6 +1100,9 @@
       <c r="O14" s="5">
         <v>20822.020304664984</v>
       </c>
+      <c r="P14" s="5">
+        <v>4783.1497191535946</v>
+      </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
@@ -1106,6 +1145,9 @@
       <c r="O15" s="5">
         <v>17212.445226073032</v>
       </c>
+      <c r="P15" s="5">
+        <v>4588.5834553379791</v>
+      </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
@@ -1148,8 +1190,11 @@
       <c r="O16" s="5">
         <v>17320.053746271926</v>
       </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="5">
+        <v>4916.5861203452214</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <f t="shared" si="0"/>
         <v>2039</v>
@@ -1190,8 +1235,11 @@
       <c r="O17" s="5">
         <v>17837.796468745979</v>
       </c>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="5">
+        <v>5019.9805142250516</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <f t="shared" si="0"/>
         <v>2040</v>
@@ -1232,8 +1280,11 @@
       <c r="O18" s="5">
         <v>11975.156503692111</v>
       </c>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="5">
+        <v>4920.7162956289676</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <f t="shared" si="0"/>
         <v>2041</v>
@@ -1274,8 +1325,11 @@
       <c r="O19" s="5">
         <v>17751.944353503422</v>
       </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="5">
+        <v>360.98095129417698</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <f t="shared" si="0"/>
         <v>2042</v>
@@ -1316,8 +1370,11 @@
       <c r="O20" s="5">
         <v>38535.962917223864</v>
       </c>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P20" s="5">
+        <v>5078.8990599726149</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <f t="shared" si="0"/>
         <v>2043</v>
@@ -1358,8 +1415,11 @@
       <c r="O21" s="5">
         <v>28948.361031309589</v>
       </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P21" s="5">
+        <v>5003.3144333855935</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <f t="shared" si="0"/>
         <v>2044</v>
@@ -1400,8 +1460,11 @@
       <c r="O22" s="5">
         <v>8308.653322847611</v>
       </c>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="5">
+        <v>4604.5350046437406</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <f t="shared" si="0"/>
         <v>2045</v>
@@ -1442,8 +1505,11 @@
       <c r="O23" s="5">
         <v>10974.815190337027</v>
       </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="5">
+        <v>666.92551687388755</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <f t="shared" si="0"/>
         <v>2046</v>
@@ -1484,8 +1550,11 @@
       <c r="O24" s="5">
         <v>12390.409145349473</v>
       </c>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="5">
+        <v>5198.4520397199713</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
         <f t="shared" si="0"/>
         <v>2047</v>
@@ -1526,8 +1595,11 @@
       <c r="O25" s="5">
         <v>42832.694420480984</v>
       </c>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="5">
+        <v>5169.330750169589</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <f t="shared" si="0"/>
         <v>2048</v>
@@ -1568,8 +1640,11 @@
       <c r="O26" s="5">
         <v>14187.758292172577</v>
       </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="5">
+        <v>5084.1899391018915</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
         <f t="shared" si="0"/>
         <v>2049</v>
@@ -1610,8 +1685,11 @@
       <c r="O27" s="5">
         <v>7000.1831282626235</v>
       </c>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="5">
+        <v>797.66075767209918</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <f t="shared" si="0"/>
         <v>2050</v>
@@ -1652,8 +1730,11 @@
       <c r="O28" s="5">
         <v>6676.8255862494798</v>
       </c>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="5">
+        <v>5375.1098812901419</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <f t="shared" si="0"/>
         <v>2051</v>
@@ -1694,8 +1775,11 @@
       <c r="O29" s="5">
         <v>9971.7076869591474</v>
       </c>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="5">
+        <v>5353.2814011403279</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <f t="shared" si="0"/>
         <v>2052</v>
@@ -1736,8 +1820,11 @@
       <c r="O30" s="5">
         <v>7192.4997346401542</v>
       </c>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P30" s="5">
+        <v>5263.8547664354483</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <f t="shared" si="0"/>
         <v>2053</v>
@@ -1774,8 +1861,11 @@
       </c>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="5">
+        <v>767.23604939946858</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <f t="shared" si="0"/>
         <v>2054</v>
@@ -1810,8 +1900,11 @@
       </c>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P32" s="5">
+        <v>5571.5249487045548</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <f t="shared" si="0"/>
         <v>2055</v>
@@ -1846,8 +1939,11 @@
       </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P33" s="5">
+        <v>5549.7131387724294</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <f t="shared" si="0"/>
         <v>2056</v>
@@ -1880,8 +1976,11 @@
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P34" s="5">
+        <v>5450.7016879833645</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <f t="shared" si="0"/>
         <v>2057</v>
@@ -1914,8 +2013,11 @@
       </c>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P35" s="5">
+        <v>2879.9434584403371</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <f t="shared" si="0"/>
         <v>2058</v>
@@ -1948,8 +2050,11 @@
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P36" s="5">
+        <v>5621.2451766894319</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <f t="shared" si="0"/>
         <v>2059</v>
@@ -1981,8 +2086,11 @@
         <v>6789.068861663226</v>
       </c>
       <c r="N37" s="5"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P37" s="5">
+        <v>5591.7311528465534</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <f t="shared" si="0"/>
         <v>2060</v>
@@ -2014,6 +2122,126 @@
         <v>7094.5769604380703</v>
       </c>
       <c r="N38" s="5"/>
+      <c r="P38" s="5">
+        <v>5476.9068357201604</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="1">
+        <f t="shared" si="0"/>
+        <v>2061</v>
+      </c>
+      <c r="P39" s="5">
+        <v>5348.2272170671049</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B40" s="1">
+        <f t="shared" si="0"/>
+        <v>2062</v>
+      </c>
+      <c r="P40" s="5">
+        <v>1553.2336857992693</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B41" s="1">
+        <f t="shared" si="0"/>
+        <v>2063</v>
+      </c>
+      <c r="P41" s="5">
+        <v>909.18588412752399</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B42" s="1">
+        <f t="shared" si="0"/>
+        <v>2064</v>
+      </c>
+      <c r="P42" s="5">
+        <v>979.22413150273474</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B43" s="1">
+        <f t="shared" si="0"/>
+        <v>2065</v>
+      </c>
+      <c r="P43" s="5">
+        <v>1021.2623014546363</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B44" s="1">
+        <f t="shared" si="0"/>
+        <v>2066</v>
+      </c>
+      <c r="P44" s="5">
+        <v>1379.6140429142242</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B45" s="1">
+        <f t="shared" si="0"/>
+        <v>2067</v>
+      </c>
+      <c r="P45" s="5">
+        <v>1547.7967575566656</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B46" s="1">
+        <f t="shared" si="0"/>
+        <v>2068</v>
+      </c>
+      <c r="P46" s="5">
+        <v>1570.2412897753873</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B47" s="1">
+        <f t="shared" si="0"/>
+        <v>2069</v>
+      </c>
+      <c r="P47" s="5">
+        <v>1562.2017608722449</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B48" s="1">
+        <f t="shared" si="0"/>
+        <v>2070</v>
+      </c>
+      <c r="P48" s="5">
+        <v>1927.3788383884005</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B49" s="1">
+        <f t="shared" si="0"/>
+        <v>2071</v>
+      </c>
+      <c r="P49" s="5">
+        <v>2073.2497657520421</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B50" s="1">
+        <f t="shared" si="0"/>
+        <v>2072</v>
+      </c>
+      <c r="P50" s="5">
+        <v>2049.4625634370504</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B51" s="1">
+        <f t="shared" si="0"/>
+        <v>2073</v>
+      </c>
+      <c r="P51" s="5">
+        <v>63753.995200912759</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2065,8 +2293,12 @@
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="11"/>
-      <c r="D7" s="12"/>
+      <c r="C7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="12">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" s="11" t="s">
@@ -2126,6 +2358,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020E4BAF79DB213408BB296F3F8F32329" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9679123e7a51fb6c2fee49c985862cfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457" xmlns:ns3="f0bab05a-e9c1-4e32-93e9-8363aec9c620" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ddaff962f7439efafa6fc254a8996caa" ns2:_="" ns3:_="">
     <xsd:import namespace="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
@@ -2360,27 +2612,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47140DD7-5C12-4BA5-9C24-A1CF0564C7A2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
+    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2397,23 +2648,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47140DD7-5C12-4BA5-9C24-A1CF0564C7A2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
-    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/irrdash3.xlsx
+++ b/irrdash3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.russo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A117E90-2A1A-49EA-81DD-B89ADA894169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C908AEC7-82CC-4456-83A8-B05AE34A3759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -655,7 +655,7 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5">
-        <v>-8.7620158507064616</v>
+        <v>-33.369646499970202</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5">
@@ -672,7 +672,7 @@
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5">
-        <v>18979.748191630773</v>
+        <v>18154.283941990547</v>
       </c>
       <c r="P4" s="5">
         <v>782.53782767150824</v>
@@ -697,7 +697,7 @@
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
-        <v>952.98742767157978</v>
+        <v>945.79818646928391</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5">
@@ -714,7 +714,7 @@
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5">
-        <v>18413.86475407553</v>
+        <v>17391.528727710025</v>
       </c>
       <c r="P5" s="5">
         <v>-388.56802401671359</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
-        <v>6589.9422482750315</v>
+        <v>6557.9529398169179</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5">
@@ -756,7 +756,7 @@
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5">
-        <v>15989.244257070595</v>
+        <v>17275.959006140532</v>
       </c>
       <c r="P6" s="5">
         <v>749.7765817929162</v>
@@ -781,7 +781,7 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
-        <v>5536.1237456745603</v>
+        <v>5530.0106092427113</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5">
@@ -798,7 +798,7 @@
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5">
-        <v>14727.36986785778</v>
+        <v>16777.150311222227</v>
       </c>
       <c r="P7" s="5">
         <v>1128.9045609814541</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
-        <v>12017.286584211188</v>
+        <v>11999.358969708313</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5">
@@ -840,7 +840,7 @@
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5">
-        <v>8099.5534825768154</v>
+        <v>9464.9753720626159</v>
       </c>
       <c r="P8" s="5">
         <v>1097.1357449407799</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
-        <v>8473.7455168781198</v>
+        <v>8502.3202806887894</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5">
@@ -882,7 +882,7 @@
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5">
-        <v>16443.830669127274</v>
+        <v>18774.394370248789</v>
       </c>
       <c r="P9" s="5">
         <v>-1187.7051190379329</v>
@@ -907,7 +907,7 @@
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
-        <v>11404.257473885451</v>
+        <v>11437.369803311882</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5">
@@ -924,7 +924,7 @@
       </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5">
-        <v>16459.568026111487</v>
+        <v>18793.920058919241</v>
       </c>
       <c r="P10" s="5">
         <v>3053.4660067585714</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
-        <v>9338.3280772234048</v>
+        <v>9367.1186753905276</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5">
@@ -966,7 +966,7 @@
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5">
-        <v>16914.43077495979</v>
+        <v>19546.493592582527</v>
       </c>
       <c r="P11" s="5">
         <v>4211.1594704752606</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
-        <v>9426.7694638763442</v>
+        <v>9452.1549622538696</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5">
-        <v>20543.191589300575</v>
+        <v>22906.932338706727</v>
       </c>
       <c r="P12" s="5">
         <v>4624.3053049833024</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5">
-        <v>9290.320997467421</v>
+        <v>9311.4050135036359</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5">
-        <v>17790.242781651366</v>
+        <v>19834.36756570905</v>
       </c>
       <c r="P13" s="5">
         <v>503.05313709281</v>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
-        <v>8673.6495661046774</v>
+        <v>8693.8319057996232</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5">
-        <v>20822.020304664984</v>
+        <v>23172.519693420705</v>
       </c>
       <c r="P14" s="5">
         <v>4783.1497191535946</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
-        <v>8188.6870790363791</v>
+        <v>8205.6637070233555</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5">
-        <v>17212.445226073032</v>
+        <v>19093.968625236597</v>
       </c>
       <c r="P15" s="5">
         <v>4588.5834553379791</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
-        <v>8004.3987166707338</v>
+        <v>8017.5741443250281</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5">
-        <v>17320.053746271926</v>
+        <v>19576.754547552948</v>
       </c>
       <c r="P16" s="5">
         <v>4916.5861203452214</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
-        <v>7114.7800115611963</v>
+        <v>7137.4138366584875</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5">
-        <v>17837.796468745979</v>
+        <v>21609.184046806968</v>
       </c>
       <c r="P17" s="5">
         <v>5019.9805142250516</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
-        <v>8959.0426799030829</v>
+        <v>8980.1275516973528</v>
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5">
-        <v>11975.156503692111</v>
+        <v>15273.079896206038</v>
       </c>
       <c r="P18" s="5">
         <v>4920.7162956289676</v>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
-        <v>5706.5892170742209</v>
+        <v>5732.097419593264</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5">
-        <v>17751.944353503422</v>
+        <v>21734.520070184193</v>
       </c>
       <c r="P19" s="5">
         <v>360.98095129417698</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5">
-        <v>5791.5387040282367</v>
+        <v>5811.7509182271833</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5">
-        <v>38535.962917223864</v>
+        <v>55786.383380606916</v>
       </c>
       <c r="P20" s="5">
         <v>5078.8990599726149</v>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
-        <v>3723.3268802003786</v>
+        <v>3757.2169130782177</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5">
-        <v>28948.361031309589</v>
+        <v>40989.969935024616</v>
       </c>
       <c r="P21" s="5">
         <v>5003.3144333855935</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5">
-        <v>2227.0346985504361</v>
+        <v>2236.9306262033019</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5">
-        <v>8308.653322847611</v>
+        <v>10669.372262431198</v>
       </c>
       <c r="P22" s="5">
         <v>4604.5350046437406</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
-        <v>661.03155598403737</v>
+        <v>709.61701460315771</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5">
-        <v>10974.815190337027</v>
+        <v>12998.05038629579</v>
       </c>
       <c r="P23" s="5">
         <v>666.92551687388755</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
-        <v>-649.48826947455473</v>
+        <v>-576.59002539919004</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5">
-        <v>12390.409145349473</v>
+        <v>14467.057314251977</v>
       </c>
       <c r="P24" s="5">
         <v>5198.4520397199713</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5">
-        <v>-758.26620108825864</v>
+        <v>-686.0921236088891</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5">
-        <v>42832.694420480984</v>
+        <v>63406.800065584444</v>
       </c>
       <c r="P25" s="5">
         <v>5169.330750169589</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5">
-        <v>-602.83404000731252</v>
+        <v>-502.19453389810548</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5">
-        <v>14187.758292172577</v>
+        <v>16616.548416356578</v>
       </c>
       <c r="P26" s="5">
         <v>5084.1899391018915</v>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5">
-        <v>-1196.1556337972008</v>
+        <v>-1124.131568617931</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5">
-        <v>7000.1831282626235</v>
+        <v>7216.411985034285</v>
       </c>
       <c r="P27" s="5">
         <v>797.66075767209918</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5">
-        <v>-1214.4629063774044</v>
+        <v>-1143.1220725938563</v>
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5">
-        <v>6676.8255862494798</v>
+        <v>6712.9799586122381</v>
       </c>
       <c r="P28" s="5">
         <v>5375.1098812901419</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5">
-        <v>-1160.7005546345265</v>
+        <v>-1090.0302985215355</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5">
-        <v>9971.7076869591474</v>
+        <v>10527.327607841195</v>
       </c>
       <c r="P29" s="5">
         <v>5353.2814011403279</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5">
-        <v>-13756.681779200566</v>
+        <v>-13686.669908091611</v>
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5">
-        <v>7192.4997346401542</v>
+        <v>7113.3756438471264</v>
       </c>
       <c r="P30" s="5">
         <v>5263.8547664354483</v>
@@ -2358,26 +2358,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020E4BAF79DB213408BB296F3F8F32329" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9679123e7a51fb6c2fee49c985862cfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457" xmlns:ns3="f0bab05a-e9c1-4e32-93e9-8363aec9c620" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ddaff962f7439efafa6fc254a8996caa" ns2:_="" ns3:_="">
     <xsd:import namespace="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
@@ -2612,10 +2592,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
+    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2632,20 +2643,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
-    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/irrdash3.xlsx
+++ b/irrdash3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.russo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C908AEC7-82CC-4456-83A8-B05AE34A3759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF957DC-3966-437C-9813-A7DBC05D4791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -672,7 +672,7 @@
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5">
-        <v>18154.283941990547</v>
+        <v>18979.748191630773</v>
       </c>
       <c r="P4" s="5">
         <v>782.53782767150824</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5">
-        <v>17391.528727710025</v>
+        <v>18413.86475407553</v>
       </c>
       <c r="P5" s="5">
         <v>-388.56802401671359</v>
@@ -756,7 +756,7 @@
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5">
-        <v>17275.959006140532</v>
+        <v>15989.244257070595</v>
       </c>
       <c r="P6" s="5">
         <v>749.7765817929162</v>
@@ -798,7 +798,7 @@
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5">
-        <v>16777.150311222227</v>
+        <v>14727.36986785778</v>
       </c>
       <c r="P7" s="5">
         <v>1128.9045609814541</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5">
-        <v>9464.9753720626159</v>
+        <v>8099.5534825768154</v>
       </c>
       <c r="P8" s="5">
         <v>1097.1357449407799</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5">
-        <v>18774.394370248789</v>
+        <v>16443.830669127274</v>
       </c>
       <c r="P9" s="5">
         <v>-1187.7051190379329</v>
@@ -924,7 +924,7 @@
       </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5">
-        <v>18793.920058919241</v>
+        <v>16459.568026111487</v>
       </c>
       <c r="P10" s="5">
         <v>3053.4660067585714</v>
@@ -966,7 +966,7 @@
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5">
-        <v>19546.493592582527</v>
+        <v>16914.43077495979</v>
       </c>
       <c r="P11" s="5">
         <v>4211.1594704752606</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5">
-        <v>22906.932338706727</v>
+        <v>20543.191589300575</v>
       </c>
       <c r="P12" s="5">
         <v>4624.3053049833024</v>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5">
-        <v>19834.36756570905</v>
+        <v>17790.242781651366</v>
       </c>
       <c r="P13" s="5">
         <v>503.05313709281</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5">
-        <v>23172.519693420705</v>
+        <v>20822.020304664984</v>
       </c>
       <c r="P14" s="5">
         <v>4783.1497191535946</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5">
-        <v>19093.968625236597</v>
+        <v>17212.445226073032</v>
       </c>
       <c r="P15" s="5">
         <v>4588.5834553379791</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5">
-        <v>19576.754547552948</v>
+        <v>17320.053746271926</v>
       </c>
       <c r="P16" s="5">
         <v>4916.5861203452214</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5">
-        <v>21609.184046806968</v>
+        <v>17837.796468745979</v>
       </c>
       <c r="P17" s="5">
         <v>5019.9805142250516</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5">
-        <v>15273.079896206038</v>
+        <v>11975.156503692111</v>
       </c>
       <c r="P18" s="5">
         <v>4920.7162956289676</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5">
-        <v>21734.520070184193</v>
+        <v>17751.944353503422</v>
       </c>
       <c r="P19" s="5">
         <v>360.98095129417698</v>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5">
-        <v>55786.383380606916</v>
+        <v>38535.962917223864</v>
       </c>
       <c r="P20" s="5">
         <v>5078.8990599726149</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5">
-        <v>40989.969935024616</v>
+        <v>28948.361031309589</v>
       </c>
       <c r="P21" s="5">
         <v>5003.3144333855935</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5">
-        <v>10669.372262431198</v>
+        <v>8308.653322847611</v>
       </c>
       <c r="P22" s="5">
         <v>4604.5350046437406</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5">
-        <v>12998.05038629579</v>
+        <v>10974.815190337027</v>
       </c>
       <c r="P23" s="5">
         <v>666.92551687388755</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5">
-        <v>14467.057314251977</v>
+        <v>12390.409145349473</v>
       </c>
       <c r="P24" s="5">
         <v>5198.4520397199713</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5">
-        <v>63406.800065584444</v>
+        <v>42832.694420480984</v>
       </c>
       <c r="P25" s="5">
         <v>5169.330750169589</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5">
-        <v>16616.548416356578</v>
+        <v>14187.758292172577</v>
       </c>
       <c r="P26" s="5">
         <v>5084.1899391018915</v>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5">
-        <v>7216.411985034285</v>
+        <v>7000.1831282626235</v>
       </c>
       <c r="P27" s="5">
         <v>797.66075767209918</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5">
-        <v>6712.9799586122381</v>
+        <v>6676.8255862494798</v>
       </c>
       <c r="P28" s="5">
         <v>5375.1098812901419</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5">
-        <v>10527.327607841195</v>
+        <v>9971.7076869591474</v>
       </c>
       <c r="P29" s="5">
         <v>5353.2814011403279</v>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5">
-        <v>7113.3756438471264</v>
+        <v>7192.4997346401542</v>
       </c>
       <c r="P30" s="5">
         <v>5263.8547664354483</v>
@@ -2358,6 +2358,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020E4BAF79DB213408BB296F3F8F32329" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9679123e7a51fb6c2fee49c985862cfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457" xmlns:ns3="f0bab05a-e9c1-4e32-93e9-8363aec9c620" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ddaff962f7439efafa6fc254a8996caa" ns2:_="" ns3:_="">
     <xsd:import namespace="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
@@ -2592,27 +2612,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47140DD7-5C12-4BA5-9C24-A1CF0564C7A2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
+    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2629,23 +2648,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47140DD7-5C12-4BA5-9C24-A1CF0564C7A2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
-    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/irrdash3.xlsx
+++ b/irrdash3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joao.russo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF957DC-3966-437C-9813-A7DBC05D4791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E724B94-DE7A-4A78-96BB-24F8CDDB1D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -672,7 +672,7 @@
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5">
-        <v>18979.748191630773</v>
+        <v>18170.656732730546</v>
       </c>
       <c r="P4" s="5">
         <v>782.53782767150824</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5">
-        <v>18413.86475407553</v>
+        <v>17391.528727710025</v>
       </c>
       <c r="P5" s="5">
         <v>-388.56802401671359</v>
@@ -756,7 +756,7 @@
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5">
-        <v>15989.244257070595</v>
+        <v>17275.959006140532</v>
       </c>
       <c r="P6" s="5">
         <v>749.7765817929162</v>
@@ -798,7 +798,7 @@
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5">
-        <v>14727.36986785778</v>
+        <v>16777.150311222227</v>
       </c>
       <c r="P7" s="5">
         <v>1128.9045609814541</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5">
-        <v>8099.5534825768154</v>
+        <v>9464.9753720626159</v>
       </c>
       <c r="P8" s="5">
         <v>1097.1357449407799</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5">
-        <v>16443.830669127274</v>
+        <v>18774.394370248789</v>
       </c>
       <c r="P9" s="5">
         <v>-1187.7051190379329</v>
@@ -924,7 +924,7 @@
       </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5">
-        <v>16459.568026111487</v>
+        <v>18793.920058919241</v>
       </c>
       <c r="P10" s="5">
         <v>3053.4660067585714</v>
@@ -966,7 +966,7 @@
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5">
-        <v>16914.43077495979</v>
+        <v>19546.493592582527</v>
       </c>
       <c r="P11" s="5">
         <v>4211.1594704752606</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5">
-        <v>20543.191589300575</v>
+        <v>22906.932338706727</v>
       </c>
       <c r="P12" s="5">
         <v>4624.3053049833024</v>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5">
-        <v>17790.242781651366</v>
+        <v>19834.36756570905</v>
       </c>
       <c r="P13" s="5">
         <v>503.05313709281</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5">
-        <v>20822.020304664984</v>
+        <v>23172.519693420705</v>
       </c>
       <c r="P14" s="5">
         <v>4783.1497191535946</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5">
-        <v>17212.445226073032</v>
+        <v>19093.968625236597</v>
       </c>
       <c r="P15" s="5">
         <v>4588.5834553379791</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5">
-        <v>17320.053746271926</v>
+        <v>19576.754547552948</v>
       </c>
       <c r="P16" s="5">
         <v>4916.5861203452214</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5">
-        <v>17837.796468745979</v>
+        <v>21609.184046806968</v>
       </c>
       <c r="P17" s="5">
         <v>5019.9805142250516</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5">
-        <v>11975.156503692111</v>
+        <v>15273.079896206038</v>
       </c>
       <c r="P18" s="5">
         <v>4920.7162956289676</v>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5">
-        <v>17751.944353503422</v>
+        <v>21734.520070184193</v>
       </c>
       <c r="P19" s="5">
         <v>360.98095129417698</v>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5">
-        <v>38535.962917223864</v>
+        <v>55786.383380606916</v>
       </c>
       <c r="P20" s="5">
         <v>5078.8990599726149</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5">
-        <v>28948.361031309589</v>
+        <v>40989.969935024616</v>
       </c>
       <c r="P21" s="5">
         <v>5003.3144333855935</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5">
-        <v>8308.653322847611</v>
+        <v>10669.372262431198</v>
       </c>
       <c r="P22" s="5">
         <v>4604.5350046437406</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5">
-        <v>10974.815190337027</v>
+        <v>12998.05038629579</v>
       </c>
       <c r="P23" s="5">
         <v>666.92551687388755</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5">
-        <v>12390.409145349473</v>
+        <v>14467.057314251977</v>
       </c>
       <c r="P24" s="5">
         <v>5198.4520397199713</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5">
-        <v>42832.694420480984</v>
+        <v>63406.800065584444</v>
       </c>
       <c r="P25" s="5">
         <v>5169.330750169589</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5">
-        <v>14187.758292172577</v>
+        <v>16616.548416356578</v>
       </c>
       <c r="P26" s="5">
         <v>5084.1899391018915</v>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5">
-        <v>7000.1831282626235</v>
+        <v>7216.411985034285</v>
       </c>
       <c r="P27" s="5">
         <v>797.66075767209918</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5">
-        <v>6676.8255862494798</v>
+        <v>6712.9799586122381</v>
       </c>
       <c r="P28" s="5">
         <v>5375.1098812901419</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5">
-        <v>9971.7076869591474</v>
+        <v>10527.327607841195</v>
       </c>
       <c r="P29" s="5">
         <v>5353.2814011403279</v>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5">
-        <v>7192.4997346401542</v>
+        <v>7113.3756438471264</v>
       </c>
       <c r="P30" s="5">
         <v>5263.8547664354483</v>
@@ -2358,26 +2358,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010020E4BAF79DB213408BB296F3F8F32329" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9679123e7a51fb6c2fee49c985862cfe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457" xmlns:ns3="f0bab05a-e9c1-4e32-93e9-8363aec9c620" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ddaff962f7439efafa6fc254a8996caa" ns2:_="" ns3:_="">
     <xsd:import namespace="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
@@ -2612,10 +2592,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f0bab05a-e9c1-4e32-93e9-8363aec9c620" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
+    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2632,20 +2643,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{873E7543-F0E8-474C-8FBB-787032D90621}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{618C5CC8-9B8E-49D5-B2E6-D98C4C570E2E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1a4d52ec-ae83-4798-bc6c-3cf1b4f12457"/>
-    <ds:schemaRef ds:uri="f0bab05a-e9c1-4e32-93e9-8363aec9c620"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>